--- a/projects/diploma_math_modeling/results/calibration/parameters.xlsx
+++ b/projects/diploma_math_modeling/results/calibration/parameters.xlsx
@@ -672,31 +672,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>63445.67</v>
+        <v>54939.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.904</v>
+        <v>0.9287</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009146</v>
+        <v>0.006183</v>
       </c>
       <c r="E2" t="n">
-        <v>307.62</v>
+        <v>207.97</v>
       </c>
       <c r="F2" t="n">
-        <v>0.030536</v>
+        <v>0.030485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.011863</v>
+        <v>0.01188</v>
       </c>
       <c r="H2" t="n">
-        <v>0.421142</v>
+        <v>0.420709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005424</v>
+        <v>0.005397</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02771</v>
+        <v>0.02761</v>
       </c>
       <c r="K2" t="n">
         <v>0.000175</v>
@@ -719,31 +719,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38066.15</v>
+        <v>27801.63</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9742</v>
+        <v>1.0007</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005487</v>
+        <v>0.003129</v>
       </c>
       <c r="E3" t="n">
-        <v>184.56</v>
+        <v>105.24</v>
       </c>
       <c r="F3" t="n">
-        <v>0.027415</v>
+        <v>0.027369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.012773</v>
+        <v>0.012791</v>
       </c>
       <c r="H3" t="n">
-        <v>0.353793</v>
+        <v>0.353428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004495</v>
+        <v>0.004473</v>
       </c>
       <c r="J3" t="n">
-        <v>0.026619</v>
+        <v>0.026523</v>
       </c>
       <c r="K3" t="n">
         <v>0.000175</v>
@@ -766,31 +766,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>102774.42</v>
+        <v>104519.73</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6192</v>
+        <v>0.6361</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014815</v>
+        <v>0.011763</v>
       </c>
       <c r="E4" t="n">
-        <v>498.3</v>
+        <v>395.65</v>
       </c>
       <c r="F4" t="n">
-        <v>0.024858</v>
+        <v>0.024816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.014621</v>
+        <v>0.014641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.416606</v>
+        <v>0.416177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004185</v>
+        <v>0.004164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.022273</v>
+        <v>0.022192</v>
       </c>
       <c r="K4" t="n">
         <v>0.000175</v>
@@ -813,31 +813,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>242052.7</v>
+        <v>327515.21</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6341</v>
+        <v>0.6514</v>
       </c>
       <c r="D5" t="n">
-        <v>0.034892</v>
+        <v>0.036859</v>
       </c>
       <c r="E5" t="n">
-        <v>1173.6</v>
+        <v>1239.78</v>
       </c>
       <c r="F5" t="n">
-        <v>0.027777</v>
+        <v>0.02773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.010802</v>
+        <v>0.010817</v>
       </c>
       <c r="H5" t="n">
-        <v>0.325526</v>
+        <v>0.325191</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005647</v>
+        <v>0.005618</v>
       </c>
       <c r="J5" t="n">
-        <v>0.026058</v>
+        <v>0.025964</v>
       </c>
       <c r="K5" t="n">
         <v>0.000175</v>
@@ -860,31 +860,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>130134</v>
+        <v>143176.79</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7781</v>
+        <v>0.7993</v>
       </c>
       <c r="D6" t="n">
-        <v>0.018759</v>
+        <v>0.016113</v>
       </c>
       <c r="E6" t="n">
-        <v>630.96</v>
+        <v>541.98</v>
       </c>
       <c r="F6" t="n">
-        <v>0.024774</v>
+        <v>0.024733</v>
       </c>
       <c r="G6" t="n">
-        <v>0.015033</v>
+        <v>0.015054</v>
       </c>
       <c r="H6" t="n">
-        <v>0.49477</v>
+        <v>0.494261</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00526</v>
+        <v>0.005234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.030435</v>
+        <v>0.030325</v>
       </c>
       <c r="K6" t="n">
         <v>0.000175</v>
@@ -907,31 +907,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>173845.88</v>
+        <v>210654.52</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8047</v>
+        <v>0.8266</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02506</v>
+        <v>0.023708</v>
       </c>
       <c r="E7" t="n">
-        <v>842.89</v>
+        <v>797.41</v>
       </c>
       <c r="F7" t="n">
-        <v>0.029858</v>
+        <v>0.029808</v>
       </c>
       <c r="G7" t="n">
-        <v>0.012601</v>
+        <v>0.012619</v>
       </c>
       <c r="H7" t="n">
-        <v>0.488265</v>
+        <v>0.487762</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004627</v>
+        <v>0.004604</v>
       </c>
       <c r="J7" t="n">
-        <v>0.024171</v>
+        <v>0.024083</v>
       </c>
       <c r="K7" t="n">
         <v>0.000175</v>
@@ -954,31 +954,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296790.24</v>
+        <v>429817.79</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9532</v>
       </c>
       <c r="D8" t="n">
-        <v>0.042782</v>
+        <v>0.048373</v>
       </c>
       <c r="E8" t="n">
-        <v>1438.99</v>
+        <v>1627.04</v>
       </c>
       <c r="F8" t="n">
-        <v>0.019715</v>
+        <v>0.019682</v>
       </c>
       <c r="G8" t="n">
-        <v>0.016229</v>
+        <v>0.016251</v>
       </c>
       <c r="H8" t="n">
-        <v>0.38986</v>
+        <v>0.389459</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006307</v>
+        <v>0.006276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.019686</v>
+        <v>0.019615</v>
       </c>
       <c r="K8" t="n">
         <v>0.000175</v>
@@ -1001,31 +1001,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>342443.54</v>
+        <v>520159.91</v>
       </c>
       <c r="C9" t="n">
-        <v>1.111</v>
+        <v>1.1413</v>
       </c>
       <c r="D9" t="n">
-        <v>0.049363</v>
+        <v>0.05854</v>
       </c>
       <c r="E9" t="n">
-        <v>1660.34</v>
+        <v>1969.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.024674</v>
+        <v>0.024633</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00954</v>
+        <v>0.009553000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.427598</v>
+        <v>0.427158</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004749</v>
+        <v>0.004725</v>
       </c>
       <c r="J9" t="n">
-        <v>0.025307</v>
+        <v>0.025215</v>
       </c>
       <c r="K9" t="n">
         <v>0.000175</v>
@@ -1048,31 +1048,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>148118.46</v>
+        <v>170149.43</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1346</v>
+        <v>1.1656</v>
       </c>
       <c r="D10" t="n">
-        <v>0.021351</v>
+        <v>0.019149</v>
       </c>
       <c r="E10" t="n">
-        <v>718.15</v>
+        <v>644.08</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01925</v>
+        <v>0.019217</v>
       </c>
       <c r="G10" t="n">
-        <v>0.012142</v>
+        <v>0.012158</v>
       </c>
       <c r="H10" t="n">
-        <v>0.282076</v>
+        <v>0.281786</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005098</v>
+        <v>0.005072</v>
       </c>
       <c r="J10" t="n">
-        <v>0.022161</v>
+        <v>0.022081</v>
       </c>
       <c r="K10" t="n">
         <v>0.000175</v>
@@ -1095,31 +1095,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>347806.62</v>
+        <v>531049.96</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9367</v>
       </c>
       <c r="D11" t="n">
-        <v>0.050136</v>
+        <v>0.059766</v>
       </c>
       <c r="E11" t="n">
-        <v>1686.35</v>
+        <v>2010.24</v>
       </c>
       <c r="F11" t="n">
-        <v>0.020736</v>
+        <v>0.020701</v>
       </c>
       <c r="G11" t="n">
-        <v>0.010608</v>
+        <v>0.010623</v>
       </c>
       <c r="H11" t="n">
-        <v>0.340431</v>
+        <v>0.340081</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005282</v>
+        <v>0.005256</v>
       </c>
       <c r="J11" t="n">
-        <v>0.024104</v>
+        <v>0.024016</v>
       </c>
       <c r="K11" t="n">
         <v>0.000175</v>
@@ -1142,31 +1142,31 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>163166.49</v>
+        <v>193579.58</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.9336</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02352</v>
+        <v>0.021786</v>
       </c>
       <c r="E12" t="n">
-        <v>791.12</v>
+        <v>732.78</v>
       </c>
       <c r="F12" t="n">
-        <v>0.031839</v>
+        <v>0.031786</v>
       </c>
       <c r="G12" t="n">
-        <v>0.012069</v>
+        <v>0.012086</v>
       </c>
       <c r="H12" t="n">
-        <v>0.387455</v>
+        <v>0.387056</v>
       </c>
       <c r="I12" t="n">
-        <v>0.004623</v>
+        <v>0.0046</v>
       </c>
       <c r="J12" t="n">
-        <v>0.025065</v>
+        <v>0.024974</v>
       </c>
       <c r="K12" t="n">
         <v>0.000175</v>
@@ -1189,31 +1189,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>93415.39999999999</v>
+        <v>92025.78</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7176</v>
+        <v>0.7372</v>
       </c>
       <c r="D13" t="n">
-        <v>0.013466</v>
+        <v>0.010357</v>
       </c>
       <c r="E13" t="n">
-        <v>452.93</v>
+        <v>348.36</v>
       </c>
       <c r="F13" t="n">
-        <v>0.029677</v>
+        <v>0.029628</v>
       </c>
       <c r="G13" t="n">
-        <v>0.014179</v>
+        <v>0.014199</v>
       </c>
       <c r="H13" t="n">
-        <v>0.344759</v>
+        <v>0.344404</v>
       </c>
       <c r="I13" t="n">
-        <v>0.005445</v>
+        <v>0.005418</v>
       </c>
       <c r="J13" t="n">
-        <v>0.019646</v>
+        <v>0.019575</v>
       </c>
       <c r="K13" t="n">
         <v>0.000175</v>
@@ -1236,31 +1236,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>108078.19</v>
+        <v>111772.67</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0883</v>
+        <v>1.118</v>
       </c>
       <c r="D14" t="n">
-        <v>0.015579</v>
+        <v>0.012579</v>
       </c>
       <c r="E14" t="n">
-        <v>524.02</v>
+        <v>423.11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.023294</v>
+        <v>0.023255</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0133</v>
+        <v>0.013318</v>
       </c>
       <c r="H14" t="n">
-        <v>0.45071</v>
+        <v>0.450246</v>
       </c>
       <c r="I14" t="n">
-        <v>0.004683</v>
+        <v>0.00466</v>
       </c>
       <c r="J14" t="n">
-        <v>0.019913</v>
+        <v>0.019841</v>
       </c>
       <c r="K14" t="n">
         <v>0.000175</v>
@@ -1283,31 +1283,31 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>63508.47</v>
+        <v>55012.38</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8393</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009155</v>
+        <v>0.006191</v>
       </c>
       <c r="E15" t="n">
-        <v>307.92</v>
+        <v>208.24</v>
       </c>
       <c r="F15" t="n">
-        <v>0.020712</v>
+        <v>0.020678</v>
       </c>
       <c r="G15" t="n">
-        <v>0.013152</v>
+        <v>0.013171</v>
       </c>
       <c r="H15" t="n">
-        <v>0.54635</v>
+        <v>0.5457880000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004769</v>
+        <v>0.004746</v>
       </c>
       <c r="J15" t="n">
-        <v>0.027276</v>
+        <v>0.027178</v>
       </c>
       <c r="K15" t="n">
         <v>0.000175</v>
@@ -1330,31 +1330,31 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>90614.55</v>
+        <v>88365.38</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5361</v>
+        <v>0.5507</v>
       </c>
       <c r="D16" t="n">
-        <v>0.013062</v>
+        <v>0.009945000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>439.35</v>
+        <v>334.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.016634</v>
+        <v>0.016606</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01334</v>
+        <v>0.013358</v>
       </c>
       <c r="H16" t="n">
-        <v>0.339398</v>
+        <v>0.339048</v>
       </c>
       <c r="I16" t="n">
-        <v>0.006224</v>
+        <v>0.006193</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02346</v>
+        <v>0.023375</v>
       </c>
       <c r="K16" t="n">
         <v>0.000175</v>
@@ -1377,31 +1377,31 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>124547.24</v>
+        <v>135040.41</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9184</v>
+        <v>0.9434</v>
       </c>
       <c r="D17" t="n">
-        <v>0.017953</v>
+        <v>0.015198</v>
       </c>
       <c r="E17" t="n">
-        <v>603.87</v>
+        <v>511.18</v>
       </c>
       <c r="F17" t="n">
-        <v>0.023917</v>
+        <v>0.023877</v>
       </c>
       <c r="G17" t="n">
-        <v>0.014085</v>
+        <v>0.014105</v>
       </c>
       <c r="H17" t="n">
-        <v>0.357111</v>
+        <v>0.356743</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00434</v>
+        <v>0.004318</v>
       </c>
       <c r="J17" t="n">
-        <v>0.017271</v>
+        <v>0.017208</v>
       </c>
       <c r="K17" t="n">
         <v>0.000175</v>
@@ -1424,31 +1424,31 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>250046.31</v>
+        <v>342015.27</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9741</v>
+        <v>1.0007</v>
       </c>
       <c r="D18" t="n">
-        <v>0.036044</v>
+        <v>0.038491</v>
       </c>
       <c r="E18" t="n">
-        <v>1212.35</v>
+        <v>1294.67</v>
       </c>
       <c r="F18" t="n">
-        <v>0.037307</v>
+        <v>0.037244</v>
       </c>
       <c r="G18" t="n">
-        <v>0.011744</v>
+        <v>0.01176</v>
       </c>
       <c r="H18" t="n">
-        <v>0.419466</v>
+        <v>0.419034</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003533</v>
+        <v>0.003515</v>
       </c>
       <c r="J18" t="n">
-        <v>0.028544</v>
+        <v>0.028441</v>
       </c>
       <c r="K18" t="n">
         <v>0.000175</v>
@@ -1471,31 +1471,31 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>433528.27</v>
+        <v>712374.14</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7256</v>
+        <v>0.7454</v>
       </c>
       <c r="D19" t="n">
-        <v>0.062493</v>
+        <v>0.08017199999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>2101.97</v>
+        <v>2696.63</v>
       </c>
       <c r="F19" t="n">
-        <v>0.027698</v>
+        <v>0.027651</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01519</v>
+        <v>0.015211</v>
       </c>
       <c r="H19" t="n">
-        <v>0.515601</v>
+        <v>0.51507</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00646</v>
+        <v>0.006428</v>
       </c>
       <c r="J19" t="n">
-        <v>0.026432</v>
+        <v>0.026336</v>
       </c>
       <c r="K19" t="n">
         <v>0.000175</v>
@@ -1518,31 +1518,31 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>67369.08</v>
+        <v>59515.82</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0725</v>
+        <v>1.1017</v>
       </c>
       <c r="D20" t="n">
-        <v>0.009710999999999999</v>
+        <v>0.006698</v>
       </c>
       <c r="E20" t="n">
-        <v>326.64</v>
+        <v>225.29</v>
       </c>
       <c r="F20" t="n">
-        <v>0.023859</v>
+        <v>0.023819</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01509</v>
+        <v>0.015111</v>
       </c>
       <c r="H20" t="n">
-        <v>0.337076</v>
+        <v>0.336729</v>
       </c>
       <c r="I20" t="n">
-        <v>0.007436</v>
+        <v>0.007399</v>
       </c>
       <c r="J20" t="n">
-        <v>0.022797</v>
+        <v>0.022715</v>
       </c>
       <c r="K20" t="n">
         <v>0.000175</v>
@@ -1565,31 +1565,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>195427.92</v>
+        <v>246225.89</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0658</v>
+        <v>1.0948</v>
       </c>
       <c r="D21" t="n">
-        <v>0.028171</v>
+        <v>0.027711</v>
       </c>
       <c r="E21" t="n">
-        <v>947.54</v>
+        <v>932.0700000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.027823</v>
+        <v>0.027777</v>
       </c>
       <c r="G21" t="n">
-        <v>0.014474</v>
+        <v>0.014494</v>
       </c>
       <c r="H21" t="n">
-        <v>0.420322</v>
+        <v>0.419889</v>
       </c>
       <c r="I21" t="n">
-        <v>0.004774</v>
+        <v>0.00475</v>
       </c>
       <c r="J21" t="n">
-        <v>0.020826</v>
+        <v>0.02075</v>
       </c>
       <c r="K21" t="n">
         <v>0.000175</v>
@@ -1612,31 +1612,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>82695.78999999999</v>
+        <v>78222.10000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1.202</v>
+        <v>1.2348</v>
       </c>
       <c r="D22" t="n">
-        <v>0.011921</v>
+        <v>0.008803</v>
       </c>
       <c r="E22" t="n">
-        <v>400.95</v>
+        <v>296.1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.020532</v>
+        <v>0.020497</v>
       </c>
       <c r="G22" t="n">
-        <v>0.014851</v>
+        <v>0.014872</v>
       </c>
       <c r="H22" t="n">
-        <v>0.532115</v>
+        <v>0.531567</v>
       </c>
       <c r="I22" t="n">
-        <v>0.003794</v>
+        <v>0.003775</v>
       </c>
       <c r="J22" t="n">
-        <v>0.028763</v>
+        <v>0.028659</v>
       </c>
       <c r="K22" t="n">
         <v>0.000175</v>
@@ -1659,31 +1659,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>205267.37</v>
+        <v>262892.46</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1479</v>
+        <v>1.1793</v>
       </c>
       <c r="D23" t="n">
-        <v>0.029589</v>
+        <v>0.029587</v>
       </c>
       <c r="E23" t="n">
-        <v>995.24</v>
+        <v>995.15</v>
       </c>
       <c r="F23" t="n">
-        <v>0.024817</v>
+        <v>0.024775</v>
       </c>
       <c r="G23" t="n">
-        <v>0.014283</v>
+        <v>0.014303</v>
       </c>
       <c r="H23" t="n">
-        <v>0.31605</v>
+        <v>0.315725</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004842</v>
+        <v>0.004818</v>
       </c>
       <c r="J23" t="n">
-        <v>0.026739</v>
+        <v>0.026642</v>
       </c>
       <c r="K23" t="n">
         <v>0.000175</v>
@@ -1706,31 +1706,31 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>142714.07</v>
+        <v>161922.54</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1524</v>
+        <v>1.1839</v>
       </c>
       <c r="D24" t="n">
-        <v>0.020572</v>
+        <v>0.018223</v>
       </c>
       <c r="E24" t="n">
-        <v>691.95</v>
+        <v>612.9400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.026339</v>
+        <v>0.026294</v>
       </c>
       <c r="G24" t="n">
-        <v>0.018539</v>
+        <v>0.018565</v>
       </c>
       <c r="H24" t="n">
-        <v>0.334122</v>
+        <v>0.333778</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00486</v>
+        <v>0.004836</v>
       </c>
       <c r="J24" t="n">
-        <v>0.036274</v>
+        <v>0.036143</v>
       </c>
       <c r="K24" t="n">
         <v>0.000175</v>
@@ -1753,31 +1753,31 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>51467.56</v>
+        <v>41565.18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8162</v>
+        <v>0.8385</v>
       </c>
       <c r="D25" t="n">
-        <v>0.007419</v>
+        <v>0.004678</v>
       </c>
       <c r="E25" t="n">
-        <v>249.54</v>
+        <v>157.34</v>
       </c>
       <c r="F25" t="n">
-        <v>0.025615</v>
+        <v>0.025573</v>
       </c>
       <c r="G25" t="n">
-        <v>0.013485</v>
+        <v>0.013503</v>
       </c>
       <c r="H25" t="n">
-        <v>0.379982</v>
+        <v>0.379591</v>
       </c>
       <c r="I25" t="n">
-        <v>0.004931</v>
+        <v>0.004906</v>
       </c>
       <c r="J25" t="n">
-        <v>0.027024</v>
+        <v>0.026927</v>
       </c>
       <c r="K25" t="n">
         <v>0.000175</v>
@@ -1800,31 +1800,31 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>269474.38</v>
+        <v>377898.25</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2874</v>
+        <v>1.3225</v>
       </c>
       <c r="D26" t="n">
-        <v>0.038845</v>
+        <v>0.04253</v>
       </c>
       <c r="E26" t="n">
-        <v>1306.55</v>
+        <v>1430.5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.029216</v>
+        <v>0.029168</v>
       </c>
       <c r="G26" t="n">
-        <v>0.013047</v>
+        <v>0.013065</v>
       </c>
       <c r="H26" t="n">
-        <v>0.374495</v>
+        <v>0.374109</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004293</v>
+        <v>0.004272</v>
       </c>
       <c r="J26" t="n">
-        <v>0.026893</v>
+        <v>0.026796</v>
       </c>
       <c r="K26" t="n">
         <v>0.000175</v>
@@ -1847,31 +1847,31 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>107392.97</v>
+        <v>110828.82</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0491</v>
+        <v>1.0778</v>
       </c>
       <c r="D27" t="n">
-        <v>0.015481</v>
+        <v>0.012473</v>
       </c>
       <c r="E27" t="n">
-        <v>520.7</v>
+        <v>419.53</v>
       </c>
       <c r="F27" t="n">
-        <v>0.027325</v>
+        <v>0.027279</v>
       </c>
       <c r="G27" t="n">
-        <v>0.012202</v>
+        <v>0.012219</v>
       </c>
       <c r="H27" t="n">
-        <v>0.457399</v>
+        <v>0.456928</v>
       </c>
       <c r="I27" t="n">
-        <v>0.005534</v>
+        <v>0.005506</v>
       </c>
       <c r="J27" t="n">
-        <v>0.024746</v>
+        <v>0.024657</v>
       </c>
       <c r="K27" t="n">
         <v>0.000175</v>
@@ -1894,31 +1894,31 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>112073.51</v>
+        <v>117315.54</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9314</v>
+        <v>0.9568</v>
       </c>
       <c r="D28" t="n">
-        <v>0.016155</v>
+        <v>0.013203</v>
       </c>
       <c r="E28" t="n">
-        <v>543.39</v>
+        <v>444.09</v>
       </c>
       <c r="F28" t="n">
-        <v>0.028685</v>
+        <v>0.028637</v>
       </c>
       <c r="G28" t="n">
-        <v>0.011702</v>
+        <v>0.011718</v>
       </c>
       <c r="H28" t="n">
-        <v>0.419857</v>
+        <v>0.419425</v>
       </c>
       <c r="I28" t="n">
-        <v>0.005488</v>
+        <v>0.005461</v>
       </c>
       <c r="J28" t="n">
-        <v>0.028681</v>
+        <v>0.028577</v>
       </c>
       <c r="K28" t="n">
         <v>0.000175</v>
@@ -1941,31 +1941,31 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>81259.17</v>
+        <v>76415.49000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>1.126</v>
+        <v>1.1567</v>
       </c>
       <c r="D29" t="n">
-        <v>0.011713</v>
+        <v>0.0086</v>
       </c>
       <c r="E29" t="n">
-        <v>393.99</v>
+        <v>289.26</v>
       </c>
       <c r="F29" t="n">
-        <v>0.023403</v>
+        <v>0.023364</v>
       </c>
       <c r="G29" t="n">
-        <v>0.011336</v>
+        <v>0.011351</v>
       </c>
       <c r="H29" t="n">
-        <v>0.310263</v>
+        <v>0.309944</v>
       </c>
       <c r="I29" t="n">
-        <v>0.004054</v>
+        <v>0.004034</v>
       </c>
       <c r="J29" t="n">
-        <v>0.027868</v>
+        <v>0.027767</v>
       </c>
       <c r="K29" t="n">
         <v>0.000175</v>
@@ -1988,31 +1988,31 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>104263.9</v>
+        <v>106544.29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8607</v>
+        <v>0.8841</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01503</v>
+        <v>0.011991</v>
       </c>
       <c r="E30" t="n">
-        <v>505.53</v>
+        <v>403.31</v>
       </c>
       <c r="F30" t="n">
-        <v>0.029689</v>
+        <v>0.02964</v>
       </c>
       <c r="G30" t="n">
-        <v>0.011957</v>
+        <v>0.011973</v>
       </c>
       <c r="H30" t="n">
-        <v>0.437456</v>
+        <v>0.437006</v>
       </c>
       <c r="I30" t="n">
-        <v>0.005634</v>
+        <v>0.005606</v>
       </c>
       <c r="J30" t="n">
-        <v>0.030614</v>
+        <v>0.030504</v>
       </c>
       <c r="K30" t="n">
         <v>0.000175</v>
@@ -2035,31 +2035,31 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>199582.84</v>
+        <v>253230.4</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0127</v>
+        <v>1.0404</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02877</v>
+        <v>0.028499</v>
       </c>
       <c r="E31" t="n">
-        <v>967.6799999999999</v>
+        <v>958.58</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03313</v>
+        <v>0.033075</v>
       </c>
       <c r="G31" t="n">
-        <v>0.013518</v>
+        <v>0.013537</v>
       </c>
       <c r="H31" t="n">
-        <v>0.371309</v>
+        <v>0.370927</v>
       </c>
       <c r="I31" t="n">
-        <v>0.006902</v>
+        <v>0.006868</v>
       </c>
       <c r="J31" t="n">
-        <v>0.023465</v>
+        <v>0.02338</v>
       </c>
       <c r="K31" t="n">
         <v>0.000175</v>
@@ -2082,31 +2082,31 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>137820</v>
+        <v>154561.47</v>
       </c>
       <c r="C32" t="n">
-        <v>1.2367</v>
+        <v>1.2704</v>
       </c>
       <c r="D32" t="n">
-        <v>0.019867</v>
+        <v>0.017395</v>
       </c>
       <c r="E32" t="n">
-        <v>668.22</v>
+        <v>585.08</v>
       </c>
       <c r="F32" t="n">
-        <v>0.022434</v>
+        <v>0.022397</v>
       </c>
       <c r="G32" t="n">
-        <v>0.014364</v>
+        <v>0.014384</v>
       </c>
       <c r="H32" t="n">
-        <v>0.490209</v>
+        <v>0.489705</v>
       </c>
       <c r="I32" t="n">
-        <v>0.005206</v>
+        <v>0.00518</v>
       </c>
       <c r="J32" t="n">
-        <v>0.023769</v>
+        <v>0.023684</v>
       </c>
       <c r="K32" t="n">
         <v>0.000175</v>
@@ -2129,31 +2129,31 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>188047.07</v>
+        <v>233905.45</v>
       </c>
       <c r="C33" t="n">
-        <v>1.3864</v>
+        <v>1.4242</v>
       </c>
       <c r="D33" t="n">
-        <v>0.027107</v>
+        <v>0.026324</v>
       </c>
       <c r="E33" t="n">
-        <v>911.75</v>
+        <v>885.4299999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.022713</v>
+        <v>0.022675</v>
       </c>
       <c r="G33" t="n">
-        <v>0.013767</v>
+        <v>0.013786</v>
       </c>
       <c r="H33" t="n">
-        <v>0.368532</v>
+        <v>0.368152</v>
       </c>
       <c r="I33" t="n">
-        <v>0.004823</v>
+        <v>0.004799</v>
       </c>
       <c r="J33" t="n">
-        <v>0.023614</v>
+        <v>0.023529</v>
       </c>
       <c r="K33" t="n">
         <v>0.000175</v>
@@ -2176,31 +2176,31 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>191837.42</v>
+        <v>240212.72</v>
       </c>
       <c r="C34" t="n">
-        <v>1.4211</v>
+        <v>1.4598</v>
       </c>
       <c r="D34" t="n">
-        <v>0.027653</v>
+        <v>0.027034</v>
       </c>
       <c r="E34" t="n">
-        <v>930.13</v>
+        <v>909.3</v>
       </c>
       <c r="F34" t="n">
-        <v>0.031705</v>
+        <v>0.031652</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01218</v>
+        <v>0.012197</v>
       </c>
       <c r="H34" t="n">
-        <v>0.368033</v>
+        <v>0.367654</v>
       </c>
       <c r="I34" t="n">
-        <v>0.004966</v>
+        <v>0.004942</v>
       </c>
       <c r="J34" t="n">
-        <v>0.028569</v>
+        <v>0.028466</v>
       </c>
       <c r="K34" t="n">
         <v>0.000175</v>
@@ -2223,31 +2223,31 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>341003.28</v>
+        <v>517245.03</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0036</v>
+        <v>1.031</v>
       </c>
       <c r="D35" t="n">
-        <v>0.049155</v>
+        <v>0.058212</v>
       </c>
       <c r="E35" t="n">
-        <v>1653.36</v>
+        <v>1957.98</v>
       </c>
       <c r="F35" t="n">
-        <v>0.025214</v>
+        <v>0.025172</v>
       </c>
       <c r="G35" t="n">
-        <v>0.015637</v>
+        <v>0.015659</v>
       </c>
       <c r="H35" t="n">
-        <v>0.439147</v>
+        <v>0.438695</v>
       </c>
       <c r="I35" t="n">
-        <v>0.005564</v>
+        <v>0.005536</v>
       </c>
       <c r="J35" t="n">
-        <v>0.031768</v>
+        <v>0.031653</v>
       </c>
       <c r="K35" t="n">
         <v>0.000175</v>
@@ -2270,31 +2270,31 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>125690.61</v>
+        <v>136695.86</v>
       </c>
       <c r="C36" t="n">
-        <v>1.0203</v>
+        <v>1.0481</v>
       </c>
       <c r="D36" t="n">
-        <v>0.018118</v>
+        <v>0.015384</v>
       </c>
       <c r="E36" t="n">
-        <v>609.41</v>
+        <v>517.45</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03203</v>
+        <v>0.031977</v>
       </c>
       <c r="G36" t="n">
-        <v>0.015264</v>
+        <v>0.015285</v>
       </c>
       <c r="H36" t="n">
-        <v>0.454003</v>
+        <v>0.453536</v>
       </c>
       <c r="I36" t="n">
-        <v>0.003913</v>
+        <v>0.003894</v>
       </c>
       <c r="J36" t="n">
-        <v>0.023686</v>
+        <v>0.0236</v>
       </c>
       <c r="K36" t="n">
         <v>0.000175</v>
@@ -2317,31 +2317,31 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>63648.8</v>
+        <v>55174.51</v>
       </c>
       <c r="C37" t="n">
-        <v>1.2999</v>
+        <v>1.3353</v>
       </c>
       <c r="D37" t="n">
-        <v>0.009175000000000001</v>
+        <v>0.006209</v>
       </c>
       <c r="E37" t="n">
-        <v>308.6</v>
+        <v>208.86</v>
       </c>
       <c r="F37" t="n">
-        <v>0.024282</v>
+        <v>0.024241</v>
       </c>
       <c r="G37" t="n">
-        <v>0.013339</v>
+        <v>0.013357</v>
       </c>
       <c r="H37" t="n">
-        <v>0.433062</v>
+        <v>0.432616</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0052</v>
+        <v>0.005174</v>
       </c>
       <c r="J37" t="n">
-        <v>0.023807</v>
+        <v>0.023721</v>
       </c>
       <c r="K37" t="n">
         <v>0.000175</v>
@@ -2364,31 +2364,31 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>292899.21</v>
+        <v>422320.84</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8145</v>
+        <v>0.8367</v>
       </c>
       <c r="D38" t="n">
-        <v>0.042221</v>
+        <v>0.047529</v>
       </c>
       <c r="E38" t="n">
-        <v>1420.13</v>
+        <v>1598.66</v>
       </c>
       <c r="F38" t="n">
-        <v>0.032277</v>
+        <v>0.032223</v>
       </c>
       <c r="G38" t="n">
-        <v>0.012387</v>
+        <v>0.012404</v>
       </c>
       <c r="H38" t="n">
-        <v>0.31445</v>
+        <v>0.314126</v>
       </c>
       <c r="I38" t="n">
-        <v>0.004785</v>
+        <v>0.004761</v>
       </c>
       <c r="J38" t="n">
-        <v>0.026598</v>
+        <v>0.026502</v>
       </c>
       <c r="K38" t="n">
         <v>0.000175</v>
@@ -2411,31 +2411,31 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>126545.54</v>
+        <v>137936.97</v>
       </c>
       <c r="C39" t="n">
-        <v>1.3374</v>
+        <v>1.3739</v>
       </c>
       <c r="D39" t="n">
-        <v>0.018241</v>
+        <v>0.015524</v>
       </c>
       <c r="E39" t="n">
-        <v>613.5599999999999</v>
+        <v>522.15</v>
       </c>
       <c r="F39" t="n">
-        <v>0.026465</v>
+        <v>0.026421</v>
       </c>
       <c r="G39" t="n">
-        <v>0.014833</v>
+        <v>0.014854</v>
       </c>
       <c r="H39" t="n">
-        <v>0.438944</v>
+        <v>0.438491</v>
       </c>
       <c r="I39" t="n">
-        <v>0.006694</v>
+        <v>0.00666</v>
       </c>
       <c r="J39" t="n">
-        <v>0.024455</v>
+        <v>0.024367</v>
       </c>
       <c r="K39" t="n">
         <v>0.000175</v>
@@ -2458,31 +2458,31 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>301343.43</v>
+        <v>438632.24</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9941</v>
+        <v>1.0213</v>
       </c>
       <c r="D40" t="n">
-        <v>0.043439</v>
+        <v>0.049365</v>
       </c>
       <c r="E40" t="n">
-        <v>1461.07</v>
+        <v>1660.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.026973</v>
+        <v>0.026928</v>
       </c>
       <c r="G40" t="n">
-        <v>0.014053</v>
+        <v>0.014072</v>
       </c>
       <c r="H40" t="n">
-        <v>0.346721</v>
+        <v>0.346364</v>
       </c>
       <c r="I40" t="n">
-        <v>0.004942</v>
+        <v>0.004918</v>
       </c>
       <c r="J40" t="n">
-        <v>0.029269</v>
+        <v>0.029163</v>
       </c>
       <c r="K40" t="n">
         <v>0.000175</v>
@@ -2505,31 +2505,31 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>194322.93</v>
+        <v>244371.37</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6159</v>
+        <v>0.6327</v>
       </c>
       <c r="D41" t="n">
-        <v>0.028012</v>
+        <v>0.027502</v>
       </c>
       <c r="E41" t="n">
-        <v>942.1799999999999</v>
+        <v>925.05</v>
       </c>
       <c r="F41" t="n">
-        <v>0.032813</v>
+        <v>0.032758</v>
       </c>
       <c r="G41" t="n">
-        <v>0.010995</v>
+        <v>0.01101</v>
       </c>
       <c r="H41" t="n">
-        <v>0.419455</v>
+        <v>0.419023</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006515</v>
+        <v>0.006483</v>
       </c>
       <c r="J41" t="n">
-        <v>0.018101</v>
+        <v>0.018035</v>
       </c>
       <c r="K41" t="n">
         <v>0.000175</v>
@@ -2552,31 +2552,31 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>142709.71</v>
+        <v>161915.95</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5877</v>
       </c>
       <c r="D42" t="n">
-        <v>0.020572</v>
+        <v>0.018222</v>
       </c>
       <c r="E42" t="n">
-        <v>691.9299999999999</v>
+        <v>612.92</v>
       </c>
       <c r="F42" t="n">
-        <v>0.024578</v>
+        <v>0.024537</v>
       </c>
       <c r="G42" t="n">
-        <v>0.013523</v>
+        <v>0.013542</v>
       </c>
       <c r="H42" t="n">
-        <v>0.327047</v>
+        <v>0.326711</v>
       </c>
       <c r="I42" t="n">
-        <v>0.004299</v>
+        <v>0.004278</v>
       </c>
       <c r="J42" t="n">
-        <v>0.022415</v>
+        <v>0.022333</v>
       </c>
       <c r="K42" t="n">
         <v>0.000175</v>
@@ -2690,28 +2690,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>147478.04</v>
+        <v>52196.31</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8083</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027623</v>
+        <v>0.023171</v>
       </c>
       <c r="E2" t="n">
-        <v>166.76</v>
+        <v>139.88</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007258</v>
+        <v>0.00723</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002802</v>
+        <v>0.002805</v>
       </c>
       <c r="H2" t="n">
-        <v>0.230048</v>
+        <v>0.230462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.072502</v>
+        <v>0.073089</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2737,28 +2737,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>58610.59</v>
+        <v>15251.23</v>
       </c>
       <c r="C3" t="n">
-        <v>0.858</v>
+        <v>0.9604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.010978</v>
+        <v>0.00677</v>
       </c>
       <c r="E3" t="n">
-        <v>66.27</v>
+        <v>40.87</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008265</v>
+        <v>0.008233000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002651</v>
+        <v>0.002654</v>
       </c>
       <c r="H3" t="n">
-        <v>0.272067</v>
+        <v>0.272556</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09668599999999999</v>
+        <v>0.097469</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2784,28 +2784,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>132283.32</v>
+        <v>45151.98</v>
       </c>
       <c r="C4" t="n">
-        <v>0.794</v>
+        <v>0.8887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.024777</v>
+        <v>0.020044</v>
       </c>
       <c r="E4" t="n">
-        <v>149.58</v>
+        <v>121.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00682</v>
+        <v>0.006794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002247</v>
+        <v>0.002249</v>
       </c>
       <c r="H4" t="n">
-        <v>0.274671</v>
+        <v>0.275165</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06546399999999999</v>
+        <v>0.065993</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2831,28 +2831,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>136187.88</v>
+        <v>46937.64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9839</v>
+        <v>1.1013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.025508</v>
+        <v>0.020837</v>
       </c>
       <c r="E5" t="n">
-        <v>153.99</v>
+        <v>125.79</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00597</v>
+        <v>0.005946</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002648</v>
+        <v>0.00265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.273299</v>
+        <v>0.27379</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05673</v>
+        <v>0.057189</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2878,28 +2878,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>209027.59</v>
+        <v>83101.37</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1466</v>
+        <v>1.2834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.039151</v>
+        <v>0.03689</v>
       </c>
       <c r="E6" t="n">
-        <v>236.36</v>
+        <v>222.71</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005521</v>
+        <v>0.005499</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002166</v>
+        <v>0.002168</v>
       </c>
       <c r="H6" t="n">
-        <v>0.235693</v>
+        <v>0.236116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.058941</v>
+        <v>0.059418</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2925,28 +2925,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>459853.79</v>
+        <v>237773.28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7826</v>
+        <v>0.876</v>
       </c>
       <c r="D7" t="n">
-        <v>0.086131</v>
+        <v>0.105552</v>
       </c>
       <c r="E7" t="n">
-        <v>519.98</v>
+        <v>637.22</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006323</v>
+        <v>0.006298</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002229</v>
+        <v>0.002231</v>
       </c>
       <c r="H7" t="n">
-        <v>0.206425</v>
+        <v>0.206796</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07827099999999999</v>
+        <v>0.078904</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2972,28 +2972,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>203586.84</v>
+        <v>80229.91</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8646</v>
+        <v>0.9678</v>
       </c>
       <c r="D8" t="n">
-        <v>0.038132</v>
+        <v>0.035616</v>
       </c>
       <c r="E8" t="n">
-        <v>230.21</v>
+        <v>215.01</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006035</v>
+        <v>0.006011</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001835</v>
+        <v>0.001837</v>
       </c>
       <c r="H8" t="n">
-        <v>0.199166</v>
+        <v>0.199524</v>
       </c>
       <c r="I8" t="n">
-        <v>0.078292</v>
+        <v>0.078925</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3019,28 +3019,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127057.64</v>
+        <v>42789.55</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3443</v>
+        <v>1.5047</v>
       </c>
       <c r="D9" t="n">
-        <v>0.023798</v>
+        <v>0.018995</v>
       </c>
       <c r="E9" t="n">
-        <v>143.67</v>
+        <v>114.67</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00542</v>
+        <v>0.005399</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002295</v>
+        <v>0.002297</v>
       </c>
       <c r="H9" t="n">
-        <v>0.246752</v>
+        <v>0.247195</v>
       </c>
       <c r="I9" t="n">
-        <v>0.076567</v>
+        <v>0.077186</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3066,28 +3066,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>227911.26</v>
+        <v>93259.06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6389</v>
+        <v>0.7151</v>
       </c>
       <c r="D10" t="n">
-        <v>0.042688</v>
+        <v>0.0414</v>
       </c>
       <c r="E10" t="n">
-        <v>257.71</v>
+        <v>249.93</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008583</v>
+        <v>0.008548999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002182</v>
+        <v>0.002184</v>
       </c>
       <c r="H10" t="n">
-        <v>0.248039</v>
+        <v>0.248484</v>
       </c>
       <c r="I10" t="n">
-        <v>0.093497</v>
+        <v>0.094254</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3113,28 +3113,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>442585.31</v>
+        <v>225943.23</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9686</v>
+        <v>1.0842</v>
       </c>
       <c r="D11" t="n">
-        <v>0.082897</v>
+        <v>0.100301</v>
       </c>
       <c r="E11" t="n">
-        <v>500.45</v>
+        <v>605.52</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00825</v>
+        <v>0.008218</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001778</v>
+        <v>0.00178</v>
       </c>
       <c r="H11" t="n">
-        <v>0.284232</v>
+        <v>0.284743</v>
       </c>
       <c r="I11" t="n">
-        <v>0.052189</v>
+        <v>0.052612</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3160,28 +3160,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>131309.06</v>
+        <v>44709.13</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1692</v>
+        <v>1.3088</v>
       </c>
       <c r="D12" t="n">
-        <v>0.024594</v>
+        <v>0.019847</v>
       </c>
       <c r="E12" t="n">
-        <v>148.48</v>
+        <v>119.82</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007485</v>
+        <v>0.007456</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002146</v>
+        <v>0.002148</v>
       </c>
       <c r="H12" t="n">
-        <v>0.276356</v>
+        <v>0.276852</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08269799999999999</v>
+        <v>0.083367</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -3207,28 +3207,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>136562.74</v>
+        <v>47109.99</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7204</v>
+        <v>0.8063</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025578</v>
+        <v>0.020913</v>
       </c>
       <c r="E13" t="n">
-        <v>154.42</v>
+        <v>126.25</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005498</v>
+        <v>0.005476</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002137</v>
+        <v>0.002139</v>
       </c>
       <c r="H13" t="n">
-        <v>0.229719</v>
+        <v>0.230132</v>
       </c>
       <c r="I13" t="n">
-        <v>0.098497</v>
+        <v>0.09929399999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3254,28 +3254,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>329724.82</v>
+        <v>152594.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6379</v>
+        <v>0.714</v>
       </c>
       <c r="D14" t="n">
-        <v>0.061758</v>
+        <v>0.06773999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>372.84</v>
+        <v>408.95</v>
       </c>
       <c r="F14" t="n">
-        <v>0.007176</v>
+        <v>0.007148</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002831</v>
+        <v>0.002834</v>
       </c>
       <c r="H14" t="n">
-        <v>0.194428</v>
+        <v>0.194777</v>
       </c>
       <c r="I14" t="n">
-        <v>0.065801</v>
+        <v>0.066334</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3301,28 +3301,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>206480.79</v>
+        <v>81754.10000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7106</v>
+        <v>0.7954</v>
       </c>
       <c r="D15" t="n">
-        <v>0.038674</v>
+        <v>0.036292</v>
       </c>
       <c r="E15" t="n">
-        <v>233.48</v>
+        <v>219.1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.006948</v>
+        <v>0.006921</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002473</v>
+        <v>0.002475</v>
       </c>
       <c r="H15" t="n">
-        <v>0.223369</v>
+        <v>0.223771</v>
       </c>
       <c r="I15" t="n">
-        <v>0.073614</v>
+        <v>0.07421</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -3348,28 +3348,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>347797.31</v>
+        <v>163846.93</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3351</v>
+        <v>1.4944</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06514300000000001</v>
+        <v>0.07273499999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>393.27</v>
+        <v>439.1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006745</v>
+        <v>0.006719</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002166</v>
+        <v>0.002168</v>
       </c>
       <c r="H16" t="n">
-        <v>0.242082</v>
+        <v>0.242517</v>
       </c>
       <c r="I16" t="n">
-        <v>0.069607</v>
+        <v>0.070171</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -3395,28 +3395,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>233911.07</v>
+        <v>96546.75999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.043812</v>
+        <v>0.042859</v>
       </c>
       <c r="E17" t="n">
-        <v>264.49</v>
+        <v>258.74</v>
       </c>
       <c r="F17" t="n">
-        <v>0.007613</v>
+        <v>0.007584</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002244</v>
+        <v>0.002247</v>
       </c>
       <c r="H17" t="n">
-        <v>0.227325</v>
+        <v>0.227733</v>
       </c>
       <c r="I17" t="n">
-        <v>0.068146</v>
+        <v>0.068698</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -3442,28 +3442,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>359289.06</v>
+        <v>171104.73</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7507</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06729499999999999</v>
+        <v>0.075957</v>
       </c>
       <c r="E18" t="n">
-        <v>406.27</v>
+        <v>458.56</v>
       </c>
       <c r="F18" t="n">
-        <v>0.006943</v>
+        <v>0.006916</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002177</v>
+        <v>0.002179</v>
       </c>
       <c r="H18" t="n">
-        <v>0.214865</v>
+        <v>0.215251</v>
       </c>
       <c r="I18" t="n">
-        <v>0.074208</v>
+        <v>0.074808</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -3489,28 +3489,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>126732.96</v>
+        <v>42643.82</v>
       </c>
       <c r="C19" t="n">
-        <v>0.625</v>
+        <v>0.6996</v>
       </c>
       <c r="D19" t="n">
-        <v>0.023737</v>
+        <v>0.01893</v>
       </c>
       <c r="E19" t="n">
-        <v>143.3</v>
+        <v>114.28</v>
       </c>
       <c r="F19" t="n">
-        <v>0.007053</v>
+        <v>0.007026</v>
       </c>
       <c r="G19" t="n">
-        <v>0.002097</v>
+        <v>0.002099</v>
       </c>
       <c r="H19" t="n">
-        <v>0.24338</v>
+        <v>0.243818</v>
       </c>
       <c r="I19" t="n">
-        <v>0.096537</v>
+        <v>0.097318</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -3536,28 +3536,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>234130.41</v>
+        <v>96667.49000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6885</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.043853</v>
+        <v>0.042913</v>
       </c>
       <c r="E20" t="n">
-        <v>264.74</v>
+        <v>259.07</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006945</v>
+        <v>0.006918</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001838</v>
+        <v>0.00184</v>
       </c>
       <c r="H20" t="n">
-        <v>0.217261</v>
+        <v>0.217651</v>
       </c>
       <c r="I20" t="n">
-        <v>0.102659</v>
+        <v>0.10349</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -3583,28 +3583,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>207828.88</v>
+        <v>82466.56</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0961</v>
+        <v>1.2269</v>
       </c>
       <c r="D21" t="n">
-        <v>0.038927</v>
+        <v>0.036609</v>
       </c>
       <c r="E21" t="n">
-        <v>235</v>
+        <v>221.01</v>
       </c>
       <c r="F21" t="n">
-        <v>0.006643</v>
+        <v>0.006617</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002114</v>
+        <v>0.002116</v>
       </c>
       <c r="H21" t="n">
-        <v>0.213254</v>
+        <v>0.213637</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0741</v>
+        <v>0.0747</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3630,28 +3630,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>113703.54</v>
+        <v>36900.76</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7933</v>
+        <v>0.888</v>
       </c>
       <c r="D22" t="n">
-        <v>0.021297</v>
+        <v>0.016381</v>
       </c>
       <c r="E22" t="n">
-        <v>128.57</v>
+        <v>98.89</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00483</v>
+        <v>0.004812</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001933</v>
+        <v>0.001935</v>
       </c>
       <c r="H22" t="n">
-        <v>0.245528</v>
+        <v>0.245969</v>
       </c>
       <c r="I22" t="n">
-        <v>0.103706</v>
+        <v>0.104546</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3677,28 +3677,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>92299.83</v>
+        <v>27942.88</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0554</v>
+        <v>1.1813</v>
       </c>
       <c r="D23" t="n">
-        <v>0.017288</v>
+        <v>0.012404</v>
       </c>
       <c r="E23" t="n">
-        <v>104.37</v>
+        <v>74.89</v>
       </c>
       <c r="F23" t="n">
-        <v>0.006392</v>
+        <v>0.006367</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001792</v>
+        <v>0.001794</v>
       </c>
       <c r="H23" t="n">
-        <v>0.220609</v>
+        <v>0.221006</v>
       </c>
       <c r="I23" t="n">
-        <v>0.078347</v>
+        <v>0.078981</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3724,28 +3724,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>355874.62</v>
+        <v>168940.08</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0722</v>
+        <v>1.2001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.06665600000000001</v>
+        <v>0.07499599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>402.4</v>
+        <v>452.75</v>
       </c>
       <c r="F24" t="n">
-        <v>0.005807</v>
+        <v>0.005784</v>
       </c>
       <c r="G24" t="n">
-        <v>0.002335</v>
+        <v>0.002337</v>
       </c>
       <c r="H24" t="n">
-        <v>0.24306</v>
+        <v>0.243497</v>
       </c>
       <c r="I24" t="n">
-        <v>0.101378</v>
+        <v>0.102199</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3771,28 +3771,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>191054.29</v>
+        <v>73713.28</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2795</v>
+        <v>1.4322</v>
       </c>
       <c r="D25" t="n">
-        <v>0.035785</v>
+        <v>0.032723</v>
       </c>
       <c r="E25" t="n">
-        <v>216.03</v>
+        <v>197.55</v>
       </c>
       <c r="F25" t="n">
-        <v>0.005209</v>
+        <v>0.005189</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002293</v>
+        <v>0.002295</v>
       </c>
       <c r="H25" t="n">
-        <v>0.244123</v>
+        <v>0.244562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.076847</v>
+        <v>0.077468</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3818,28 +3818,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>127709.85</v>
+        <v>43082.66</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6038</v>
+        <v>0.6758</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02392</v>
+        <v>0.019125</v>
       </c>
       <c r="E26" t="n">
-        <v>144.41</v>
+        <v>115.46</v>
       </c>
       <c r="F26" t="n">
-        <v>0.008123</v>
+        <v>0.008092</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001654</v>
+        <v>0.001656</v>
       </c>
       <c r="H26" t="n">
-        <v>0.197508</v>
+        <v>0.197863</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07947700000000001</v>
+        <v>0.08012</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3956,31 +3956,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>420.68</v>
+        <v>13500.25</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4415</v>
+        <v>1.4372</v>
       </c>
       <c r="D2" t="n">
-        <v>0.036385</v>
+        <v>0.036704</v>
       </c>
       <c r="E2" t="n">
-        <v>38.67</v>
+        <v>39.01</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002033</v>
+        <v>0.002045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.015236</v>
+        <v>0.015252</v>
       </c>
       <c r="H2" t="n">
-        <v>0.195791</v>
+        <v>0.194318</v>
       </c>
       <c r="I2" t="n">
-        <v>0.018329</v>
+        <v>0.018344</v>
       </c>
       <c r="J2" t="n">
-        <v>0.051648</v>
+        <v>0.051949</v>
       </c>
       <c r="K2" t="n">
         <v>0.000175</v>
@@ -4003,31 +4003,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>194.38</v>
+        <v>4822.55</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6207</v>
+        <v>0.6188</v>
       </c>
       <c r="D3" t="n">
-        <v>0.016812</v>
+        <v>0.013112</v>
       </c>
       <c r="E3" t="n">
-        <v>17.87</v>
+        <v>13.94</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002372</v>
+        <v>0.002386</v>
       </c>
       <c r="G3" t="n">
-        <v>0.016008</v>
+        <v>0.016024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.205723</v>
+        <v>0.204174</v>
       </c>
       <c r="I3" t="n">
-        <v>0.014349</v>
+        <v>0.014361</v>
       </c>
       <c r="J3" t="n">
-        <v>0.057193</v>
+        <v>0.057527</v>
       </c>
       <c r="K3" t="n">
         <v>0.000175</v>
@@ -4050,31 +4050,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>549.5599999999999</v>
+        <v>19279.51</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3961</v>
+        <v>1.3919</v>
       </c>
       <c r="D4" t="n">
-        <v>0.047533</v>
+        <v>0.052417</v>
       </c>
       <c r="E4" t="n">
-        <v>50.52</v>
+        <v>55.71</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002346</v>
+        <v>0.002359</v>
       </c>
       <c r="G4" t="n">
-        <v>0.016982</v>
+        <v>0.016999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.175878</v>
+        <v>0.174554</v>
       </c>
       <c r="I4" t="n">
-        <v>0.019163</v>
+        <v>0.019179</v>
       </c>
       <c r="J4" t="n">
-        <v>0.067856</v>
+        <v>0.06825199999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.000175</v>
@@ -4097,31 +4097,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>369.58</v>
+        <v>11359.09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6004</v>
+        <v>0.5986</v>
       </c>
       <c r="D5" t="n">
-        <v>0.031965</v>
+        <v>0.030883</v>
       </c>
       <c r="E5" t="n">
-        <v>33.97</v>
+        <v>32.82</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002127</v>
+        <v>0.002139</v>
       </c>
       <c r="G5" t="n">
-        <v>0.013325</v>
+        <v>0.013339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.208399</v>
+        <v>0.206831</v>
       </c>
       <c r="I5" t="n">
-        <v>0.018388</v>
+        <v>0.018403</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07993500000000001</v>
+        <v>0.080402</v>
       </c>
       <c r="K5" t="n">
         <v>0.000175</v>
@@ -4144,31 +4144,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114.36</v>
+        <v>2377.52</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7645</v>
+        <v>0.7622</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009892</v>
+        <v>0.006464</v>
       </c>
       <c r="E6" t="n">
-        <v>10.51</v>
+        <v>6.87</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002353</v>
+        <v>0.002367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.013242</v>
+        <v>0.013255</v>
       </c>
       <c r="H6" t="n">
-        <v>0.196929</v>
+        <v>0.195447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.016813</v>
+        <v>0.016827</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09995800000000001</v>
+        <v>0.100541</v>
       </c>
       <c r="K6" t="n">
         <v>0.000175</v>
@@ -4191,31 +4191,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109.88</v>
+        <v>2254.08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3465</v>
+        <v>1.3424</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009504</v>
+        <v>0.006128</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>6.51</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002217</v>
+        <v>0.00223</v>
       </c>
       <c r="G7" t="n">
-        <v>0.018271</v>
+        <v>0.01829</v>
       </c>
       <c r="H7" t="n">
-        <v>0.154593</v>
+        <v>0.153429</v>
       </c>
       <c r="I7" t="n">
-        <v>0.014769</v>
+        <v>0.014781</v>
       </c>
       <c r="J7" t="n">
-        <v>0.060062</v>
+        <v>0.060413</v>
       </c>
       <c r="K7" t="n">
         <v>0.000175</v>
@@ -4238,31 +4238,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>353.25</v>
+        <v>10694.84</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6795</v>
+        <v>0.6774</v>
       </c>
       <c r="D8" t="n">
-        <v>0.030553</v>
+        <v>0.029077</v>
       </c>
       <c r="E8" t="n">
-        <v>32.47</v>
+        <v>30.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002467</v>
+        <v>0.002481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.014552</v>
+        <v>0.014567</v>
       </c>
       <c r="H8" t="n">
-        <v>0.230988</v>
+        <v>0.229249</v>
       </c>
       <c r="I8" t="n">
-        <v>0.014556</v>
+        <v>0.014568</v>
       </c>
       <c r="J8" t="n">
-        <v>0.081342</v>
+        <v>0.081817</v>
       </c>
       <c r="K8" t="n">
         <v>0.000175</v>
@@ -4285,31 +4285,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>311.68</v>
+        <v>9050.709999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9136</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.026958</v>
+        <v>0.024607</v>
       </c>
       <c r="E9" t="n">
-        <v>28.65</v>
+        <v>26.15</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002152</v>
+        <v>0.002164</v>
       </c>
       <c r="G9" t="n">
-        <v>0.012517</v>
+        <v>0.01253</v>
       </c>
       <c r="H9" t="n">
-        <v>0.172588</v>
+        <v>0.171289</v>
       </c>
       <c r="I9" t="n">
-        <v>0.015275</v>
+        <v>0.015288</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06802900000000001</v>
+        <v>0.068426</v>
       </c>
       <c r="K9" t="n">
         <v>0.000175</v>
@@ -4332,31 +4332,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>334.46</v>
+        <v>9943.120000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9499</v>
+        <v>0.947</v>
       </c>
       <c r="D10" t="n">
-        <v>0.028928</v>
+        <v>0.027033</v>
       </c>
       <c r="E10" t="n">
-        <v>30.74</v>
+        <v>28.73</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001953</v>
+        <v>0.001964</v>
       </c>
       <c r="G10" t="n">
-        <v>0.016547</v>
+        <v>0.016563</v>
       </c>
       <c r="H10" t="n">
-        <v>0.145148</v>
+        <v>0.144055</v>
       </c>
       <c r="I10" t="n">
-        <v>0.017962</v>
+        <v>0.017977</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06411500000000001</v>
+        <v>0.064489</v>
       </c>
       <c r="K10" t="n">
         <v>0.000175</v>
@@ -4379,31 +4379,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>349.94</v>
+        <v>10561.66</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7453</v>
+        <v>0.743</v>
       </c>
       <c r="D11" t="n">
-        <v>0.030267</v>
+        <v>0.028715</v>
       </c>
       <c r="E11" t="n">
-        <v>32.17</v>
+        <v>30.52</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002167</v>
+        <v>0.002179</v>
       </c>
       <c r="G11" t="n">
-        <v>0.016595</v>
+        <v>0.016612</v>
       </c>
       <c r="H11" t="n">
-        <v>0.159057</v>
+        <v>0.15786</v>
       </c>
       <c r="I11" t="n">
-        <v>0.014347</v>
+        <v>0.014359</v>
       </c>
       <c r="J11" t="n">
-        <v>0.069983</v>
+        <v>0.070392</v>
       </c>
       <c r="K11" t="n">
         <v>0.000175</v>
@@ -4426,31 +4426,31 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>407.44</v>
+        <v>12936.65</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2102</v>
+        <v>1.2066</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03524</v>
+        <v>0.035172</v>
       </c>
       <c r="E12" t="n">
-        <v>37.45</v>
+        <v>37.38</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001327</v>
+        <v>0.001335</v>
       </c>
       <c r="G12" t="n">
-        <v>0.012305</v>
+        <v>0.012317</v>
       </c>
       <c r="H12" t="n">
-        <v>0.15963</v>
+        <v>0.158429</v>
       </c>
       <c r="I12" t="n">
-        <v>0.017681</v>
+        <v>0.017696</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06619800000000001</v>
+        <v>0.06658500000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.000175</v>
@@ -4473,31 +4473,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>628.38</v>
+        <v>23051.63</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3513</v>
+        <v>1.3472</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05435</v>
+        <v>0.06267300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>57.76</v>
+        <v>66.61</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002182</v>
+        <v>0.002194</v>
       </c>
       <c r="G13" t="n">
-        <v>0.016023</v>
+        <v>0.016039</v>
       </c>
       <c r="H13" t="n">
-        <v>0.187512</v>
+        <v>0.186101</v>
       </c>
       <c r="I13" t="n">
-        <v>0.013744</v>
+        <v>0.013756</v>
       </c>
       <c r="J13" t="n">
-        <v>0.066681</v>
+        <v>0.06707100000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.000175</v>
@@ -4520,31 +4520,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>182.71</v>
+        <v>4440.35</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3746</v>
+        <v>1.3704</v>
       </c>
       <c r="D14" t="n">
-        <v>0.015803</v>
+        <v>0.012072</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8</v>
+        <v>12.83</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001192</v>
+        <v>0.001199</v>
       </c>
       <c r="G14" t="n">
-        <v>0.017287</v>
+        <v>0.017304</v>
       </c>
       <c r="H14" t="n">
-        <v>0.178563</v>
+        <v>0.177219</v>
       </c>
       <c r="I14" t="n">
-        <v>0.016059</v>
+        <v>0.016072</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06169</v>
+        <v>0.06205</v>
       </c>
       <c r="K14" t="n">
         <v>0.000175</v>
@@ -4567,31 +4567,31 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>176.16</v>
+        <v>4229.31</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8393</v>
+        <v>0.8368</v>
       </c>
       <c r="D15" t="n">
-        <v>0.015236</v>
+        <v>0.011499</v>
       </c>
       <c r="E15" t="n">
-        <v>16.19</v>
+        <v>12.22</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001591</v>
+        <v>0.0016</v>
       </c>
       <c r="G15" t="n">
-        <v>0.016375</v>
+        <v>0.016392</v>
       </c>
       <c r="H15" t="n">
-        <v>0.176884</v>
+        <v>0.175552</v>
       </c>
       <c r="I15" t="n">
-        <v>0.016833</v>
+        <v>0.016847</v>
       </c>
       <c r="J15" t="n">
-        <v>0.053178</v>
+        <v>0.053489</v>
       </c>
       <c r="K15" t="n">
         <v>0.000175</v>
@@ -4614,31 +4614,31 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>184.67</v>
+        <v>4503.96</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0309</v>
+        <v>1.0277</v>
       </c>
       <c r="D16" t="n">
-        <v>0.015972</v>
+        <v>0.012245</v>
       </c>
       <c r="E16" t="n">
-        <v>16.98</v>
+        <v>13.01</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002205</v>
+        <v>0.002217</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01702</v>
+        <v>0.017038</v>
       </c>
       <c r="H16" t="n">
-        <v>0.204174</v>
+        <v>0.202637</v>
       </c>
       <c r="I16" t="n">
-        <v>0.023895</v>
+        <v>0.023914</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05203</v>
+        <v>0.052334</v>
       </c>
       <c r="K16" t="n">
         <v>0.000175</v>
@@ -4661,31 +4661,31 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>423.23</v>
+        <v>13609.26</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7484</v>
+        <v>0.7461</v>
       </c>
       <c r="D17" t="n">
-        <v>0.036605</v>
+        <v>0.037001</v>
       </c>
       <c r="E17" t="n">
-        <v>38.9</v>
+        <v>39.32</v>
       </c>
       <c r="F17" t="n">
-        <v>0.002213</v>
+        <v>0.002226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.012541</v>
+        <v>0.012553</v>
       </c>
       <c r="H17" t="n">
-        <v>0.195782</v>
+        <v>0.194308</v>
       </c>
       <c r="I17" t="n">
-        <v>0.013468</v>
+        <v>0.013479</v>
       </c>
       <c r="J17" t="n">
-        <v>0.072338</v>
+        <v>0.07276000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.000175</v>
@@ -4708,31 +4708,31 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>751.09</v>
+        <v>29241.08</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7448</v>
+        <v>0.7425</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06496300000000001</v>
+        <v>0.079501</v>
       </c>
       <c r="E18" t="n">
-        <v>69.04000000000001</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00173</v>
+        <v>0.00174</v>
       </c>
       <c r="G18" t="n">
-        <v>0.016269</v>
+        <v>0.016286</v>
       </c>
       <c r="H18" t="n">
-        <v>0.195083</v>
+        <v>0.193615</v>
       </c>
       <c r="I18" t="n">
-        <v>0.020649</v>
+        <v>0.020666</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06292</v>
+        <v>0.063287</v>
       </c>
       <c r="K18" t="n">
         <v>0.000175</v>
@@ -4755,31 +4755,31 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>274.72</v>
+        <v>7648.77</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6613</v>
+        <v>0.6592</v>
       </c>
       <c r="D19" t="n">
-        <v>0.023761</v>
+        <v>0.020795</v>
       </c>
       <c r="E19" t="n">
-        <v>25.25</v>
+        <v>22.1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.001851</v>
+        <v>0.001862</v>
       </c>
       <c r="G19" t="n">
-        <v>0.014794</v>
+        <v>0.014809</v>
       </c>
       <c r="H19" t="n">
-        <v>0.197847</v>
+        <v>0.196357</v>
       </c>
       <c r="I19" t="n">
-        <v>0.016935</v>
+        <v>0.016949</v>
       </c>
       <c r="J19" t="n">
-        <v>0.059976</v>
+        <v>0.060327</v>
       </c>
       <c r="K19" t="n">
         <v>0.000175</v>
@@ -4802,31 +4802,31 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>79.31999999999999</v>
+        <v>1459.74</v>
       </c>
       <c r="C20" t="n">
-        <v>1.44</v>
+        <v>1.4356</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006861</v>
+        <v>0.003969</v>
       </c>
       <c r="E20" t="n">
-        <v>7.29</v>
+        <v>4.22</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00253</v>
+        <v>0.002545</v>
       </c>
       <c r="G20" t="n">
-        <v>0.014399</v>
+        <v>0.014414</v>
       </c>
       <c r="H20" t="n">
-        <v>0.204065</v>
+        <v>0.202529</v>
       </c>
       <c r="I20" t="n">
-        <v>0.017612</v>
+        <v>0.017626</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06567000000000001</v>
+        <v>0.066053</v>
       </c>
       <c r="K20" t="n">
         <v>0.000175</v>
@@ -4849,31 +4849,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>128.02</v>
+        <v>2763.29</v>
       </c>
       <c r="C21" t="n">
-        <v>1.388</v>
+        <v>1.3838</v>
       </c>
       <c r="D21" t="n">
-        <v>0.011072</v>
+        <v>0.007513</v>
       </c>
       <c r="E21" t="n">
-        <v>11.77</v>
+        <v>7.98</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001916</v>
+        <v>0.001927</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01764</v>
+        <v>0.017658</v>
       </c>
       <c r="H21" t="n">
-        <v>0.135616</v>
+        <v>0.134595</v>
       </c>
       <c r="I21" t="n">
-        <v>0.016855</v>
+        <v>0.016869</v>
       </c>
       <c r="J21" t="n">
-        <v>0.073892</v>
+        <v>0.074323</v>
       </c>
       <c r="K21" t="n">
         <v>0.000175</v>
@@ -4896,31 +4896,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>215.88</v>
+        <v>5546.61</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2774</v>
+        <v>1.2735</v>
       </c>
       <c r="D22" t="n">
-        <v>0.018672</v>
+        <v>0.01508</v>
       </c>
       <c r="E22" t="n">
-        <v>19.84</v>
+        <v>16.03</v>
       </c>
       <c r="F22" t="n">
-        <v>0.002884</v>
+        <v>0.002901</v>
       </c>
       <c r="G22" t="n">
-        <v>0.019327</v>
+        <v>0.019347</v>
       </c>
       <c r="H22" t="n">
-        <v>0.176153</v>
+        <v>0.174827</v>
       </c>
       <c r="I22" t="n">
-        <v>0.017701</v>
+        <v>0.017715</v>
       </c>
       <c r="J22" t="n">
-        <v>0.067385</v>
+        <v>0.067778</v>
       </c>
       <c r="K22" t="n">
         <v>0.000175</v>
@@ -4943,31 +4943,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>254.66</v>
+        <v>6913.21</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0177</v>
+        <v>1.0146</v>
       </c>
       <c r="D23" t="n">
-        <v>0.022026</v>
+        <v>0.018796</v>
       </c>
       <c r="E23" t="n">
-        <v>23.41</v>
+        <v>19.98</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00206</v>
+        <v>0.002071</v>
       </c>
       <c r="G23" t="n">
-        <v>0.020262</v>
+        <v>0.020283</v>
       </c>
       <c r="H23" t="n">
-        <v>0.134154</v>
+        <v>0.133144</v>
       </c>
       <c r="I23" t="n">
-        <v>0.016181</v>
+        <v>0.016194</v>
       </c>
       <c r="J23" t="n">
-        <v>0.059439</v>
+        <v>0.059786</v>
       </c>
       <c r="K23" t="n">
         <v>0.000175</v>
@@ -4990,31 +4990,31 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>278.53</v>
+        <v>7790.51</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9906</v>
+        <v>0.9876</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02409</v>
+        <v>0.021181</v>
       </c>
       <c r="E24" t="n">
-        <v>25.6</v>
+        <v>22.51</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00219</v>
+        <v>0.002203</v>
       </c>
       <c r="G24" t="n">
-        <v>0.018856</v>
+        <v>0.018875</v>
       </c>
       <c r="H24" t="n">
-        <v>0.18706</v>
+        <v>0.185652</v>
       </c>
       <c r="I24" t="n">
-        <v>0.020594</v>
+        <v>0.020611</v>
       </c>
       <c r="J24" t="n">
-        <v>0.078831</v>
+        <v>0.079291</v>
       </c>
       <c r="K24" t="n">
         <v>0.000175</v>
@@ -5037,31 +5037,31 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>364.2</v>
+        <v>11139.33</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0297</v>
+        <v>1.0266</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0315</v>
+        <v>0.030286</v>
       </c>
       <c r="E25" t="n">
-        <v>33.48</v>
+        <v>32.19</v>
       </c>
       <c r="F25" t="n">
-        <v>0.002626</v>
+        <v>0.002641</v>
       </c>
       <c r="G25" t="n">
-        <v>0.015228</v>
+        <v>0.015244</v>
       </c>
       <c r="H25" t="n">
-        <v>0.185921</v>
+        <v>0.184522</v>
       </c>
       <c r="I25" t="n">
-        <v>0.015462</v>
+        <v>0.015475</v>
       </c>
       <c r="J25" t="n">
-        <v>0.083116</v>
+        <v>0.083602</v>
       </c>
       <c r="K25" t="n">
         <v>0.000175</v>
@@ -5084,31 +5084,31 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>295.16</v>
+        <v>8416.719999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0366</v>
+        <v>1.0334</v>
       </c>
       <c r="D26" t="n">
-        <v>0.025529</v>
+        <v>0.022883</v>
       </c>
       <c r="E26" t="n">
-        <v>27.13</v>
+        <v>24.32</v>
       </c>
       <c r="F26" t="n">
-        <v>0.002101</v>
+        <v>0.002113</v>
       </c>
       <c r="G26" t="n">
-        <v>0.016322</v>
+        <v>0.016339</v>
       </c>
       <c r="H26" t="n">
-        <v>0.217641</v>
+        <v>0.216003</v>
       </c>
       <c r="I26" t="n">
-        <v>0.019623</v>
+        <v>0.01964</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07063700000000001</v>
+        <v>0.071049</v>
       </c>
       <c r="K26" t="n">
         <v>0.000175</v>
@@ -5131,31 +5131,31 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>667.91</v>
+        <v>25005.32</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9346</v>
+        <v>0.9317</v>
       </c>
       <c r="D27" t="n">
-        <v>0.057769</v>
+        <v>0.067984</v>
       </c>
       <c r="E27" t="n">
-        <v>61.4</v>
+        <v>72.25</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001773</v>
+        <v>0.001783</v>
       </c>
       <c r="G27" t="n">
-        <v>0.017368</v>
+        <v>0.017386</v>
       </c>
       <c r="H27" t="n">
-        <v>0.22233</v>
+        <v>0.220657</v>
       </c>
       <c r="I27" t="n">
-        <v>0.015033</v>
+        <v>0.015045</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0759</v>
+        <v>0.07634299999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.000175</v>
@@ -5178,31 +5178,31 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>237.21</v>
+        <v>6289.01</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6318</v>
+        <v>0.6298</v>
       </c>
       <c r="D28" t="n">
-        <v>0.020517</v>
+        <v>0.017099</v>
       </c>
       <c r="E28" t="n">
-        <v>21.81</v>
+        <v>18.17</v>
       </c>
       <c r="F28" t="n">
-        <v>0.002026</v>
+        <v>0.002038</v>
       </c>
       <c r="G28" t="n">
-        <v>0.015765</v>
+        <v>0.015781</v>
       </c>
       <c r="H28" t="n">
-        <v>0.191796</v>
+        <v>0.190353</v>
       </c>
       <c r="I28" t="n">
-        <v>0.016409</v>
+        <v>0.016423</v>
       </c>
       <c r="J28" t="n">
-        <v>0.079017</v>
+        <v>0.07947799999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.000175</v>
@@ -5225,31 +5225,31 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>212.12</v>
+        <v>5418.19</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6257</v>
+        <v>0.6238</v>
       </c>
       <c r="D29" t="n">
-        <v>0.018347</v>
+        <v>0.014731</v>
       </c>
       <c r="E29" t="n">
-        <v>19.5</v>
+        <v>15.66</v>
       </c>
       <c r="F29" t="n">
-        <v>0.002049</v>
+        <v>0.002061</v>
       </c>
       <c r="G29" t="n">
-        <v>0.015788</v>
+        <v>0.015804</v>
       </c>
       <c r="H29" t="n">
-        <v>0.172598</v>
+        <v>0.171299</v>
       </c>
       <c r="I29" t="n">
-        <v>0.014099</v>
+        <v>0.01411</v>
       </c>
       <c r="J29" t="n">
-        <v>0.07770199999999999</v>
+        <v>0.078156</v>
       </c>
       <c r="K29" t="n">
         <v>0.000175</v>
@@ -5272,31 +5272,31 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>474.32</v>
+        <v>15842.83</v>
       </c>
       <c r="C30" t="n">
-        <v>1.4522</v>
+        <v>1.4478</v>
       </c>
       <c r="D30" t="n">
-        <v>0.041025</v>
+        <v>0.043073</v>
       </c>
       <c r="E30" t="n">
-        <v>43.6</v>
+        <v>45.78</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001679</v>
+        <v>0.001688</v>
       </c>
       <c r="G30" t="n">
-        <v>0.017517</v>
+        <v>0.017535</v>
       </c>
       <c r="H30" t="n">
-        <v>0.200095</v>
+        <v>0.198589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.017728</v>
+        <v>0.017743</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07191500000000001</v>
+        <v>0.072334</v>
       </c>
       <c r="K30" t="n">
         <v>0.000175</v>
@@ -5319,31 +5319,31 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>141.62</v>
+        <v>3161.68</v>
       </c>
       <c r="C31" t="n">
-        <v>0.982</v>
+        <v>0.979</v>
       </c>
       <c r="D31" t="n">
-        <v>0.012249</v>
+        <v>0.008595999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>13.02</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.001983</v>
+        <v>0.001994</v>
       </c>
       <c r="G31" t="n">
-        <v>0.015344</v>
+        <v>0.01536</v>
       </c>
       <c r="H31" t="n">
-        <v>0.171886</v>
+        <v>0.170592</v>
       </c>
       <c r="I31" t="n">
-        <v>0.020566</v>
+        <v>0.020583</v>
       </c>
       <c r="J31" t="n">
-        <v>0.071745</v>
+        <v>0.07216400000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.000175</v>
@@ -5366,31 +5366,31 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>449.61</v>
+        <v>14751.87</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4532</v>
+        <v>1.4488</v>
       </c>
       <c r="D32" t="n">
-        <v>0.038887</v>
+        <v>0.040107</v>
       </c>
       <c r="E32" t="n">
-        <v>41.33</v>
+        <v>42.63</v>
       </c>
       <c r="F32" t="n">
-        <v>0.001843</v>
+        <v>0.001854</v>
       </c>
       <c r="G32" t="n">
-        <v>0.013877</v>
+        <v>0.013891</v>
       </c>
       <c r="H32" t="n">
-        <v>0.186012</v>
+        <v>0.184611</v>
       </c>
       <c r="I32" t="n">
-        <v>0.016367</v>
+        <v>0.016381</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07090299999999999</v>
+        <v>0.07131700000000001</v>
       </c>
       <c r="K32" t="n">
         <v>0.000175</v>
@@ -5413,31 +5413,31 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>378.45</v>
+        <v>11724.25</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6636</v>
+        <v>0.6616</v>
       </c>
       <c r="D33" t="n">
-        <v>0.032733</v>
+        <v>0.031876</v>
       </c>
       <c r="E33" t="n">
-        <v>34.79</v>
+        <v>33.88</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002367</v>
+        <v>0.00238</v>
       </c>
       <c r="G33" t="n">
-        <v>0.014548</v>
+        <v>0.014563</v>
       </c>
       <c r="H33" t="n">
-        <v>0.215711</v>
+        <v>0.214087</v>
       </c>
       <c r="I33" t="n">
-        <v>0.016076</v>
+        <v>0.01609</v>
       </c>
       <c r="J33" t="n">
-        <v>0.055632</v>
+        <v>0.055957</v>
       </c>
       <c r="K33" t="n">
         <v>0.000175</v>
@@ -5460,31 +5460,31 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>325.74</v>
+        <v>9599.040000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0544</v>
+        <v>1.0512</v>
       </c>
       <c r="D34" t="n">
-        <v>0.028174</v>
+        <v>0.026098</v>
       </c>
       <c r="E34" t="n">
-        <v>29.94</v>
+        <v>27.74</v>
       </c>
       <c r="F34" t="n">
-        <v>0.002071</v>
+        <v>0.002083</v>
       </c>
       <c r="G34" t="n">
-        <v>0.017025</v>
+        <v>0.017043</v>
       </c>
       <c r="H34" t="n">
-        <v>0.171118</v>
+        <v>0.16983</v>
       </c>
       <c r="I34" t="n">
-        <v>0.014009</v>
+        <v>0.01402</v>
       </c>
       <c r="J34" t="n">
-        <v>0.072855</v>
+        <v>0.07328</v>
       </c>
       <c r="K34" t="n">
         <v>0.000175</v>
@@ -5507,31 +5507,31 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>922.9</v>
+        <v>38483.81</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7077</v>
+        <v>0.7056</v>
       </c>
       <c r="D35" t="n">
-        <v>0.07982300000000001</v>
+        <v>0.10463</v>
       </c>
       <c r="E35" t="n">
-        <v>84.84</v>
+        <v>111.2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.001975</v>
+        <v>0.001986</v>
       </c>
       <c r="G35" t="n">
-        <v>0.015488</v>
+        <v>0.015504</v>
       </c>
       <c r="H35" t="n">
-        <v>0.20995</v>
+        <v>0.20837</v>
       </c>
       <c r="I35" t="n">
-        <v>0.015998</v>
+        <v>0.016012</v>
       </c>
       <c r="J35" t="n">
-        <v>0.053517</v>
+        <v>0.053829</v>
       </c>
       <c r="K35" t="n">
         <v>0.000175</v>
@@ -5929,13 +5929,13 @@
         <v>10717</v>
       </c>
       <c r="G2" t="n">
-        <v>10531.1</v>
+        <v>10208.7</v>
       </c>
       <c r="H2" t="n">
         <v>10746</v>
       </c>
       <c r="I2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -5960,13 +5960,13 @@
         <v>4635</v>
       </c>
       <c r="G3" t="n">
-        <v>51474</v>
+        <v>45037</v>
       </c>
       <c r="H3" t="n">
         <v>106178</v>
       </c>
       <c r="I3" t="n">
-        <v>48.48</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="4">
@@ -6022,13 +6022,13 @@
         <v>1893</v>
       </c>
       <c r="G5" t="n">
-        <v>134096.5</v>
+        <v>7122</v>
       </c>
       <c r="H5" t="n">
         <v>297148</v>
       </c>
       <c r="I5" t="n">
-        <v>45.13</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -6138,25 +6138,25 @@
         <v>0.06</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0698</v>
+        <v>0.1395</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1252</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1583</v>
+        <v>0.1558</v>
       </c>
       <c r="H2" t="n">
         <v>0.0267</v>
       </c>
       <c r="I2" t="n">
-        <v>3550</v>
+        <v>78102</v>
       </c>
       <c r="J2" t="n">
         <v>4541</v>
@@ -6175,25 +6175,25 @@
         <v>0.04</v>
       </c>
       <c r="C3" t="n">
-        <v>62892.0157</v>
+        <v>0.1654</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F3" t="n">
         <v>0.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1833</v>
+        <v>0.1712</v>
       </c>
       <c r="H3" t="n">
         <v>0.0241</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>707256</v>
       </c>
       <c r="J3" t="n">
         <v>41118</v>
@@ -6212,25 +6212,25 @@
         <v>0.055</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2424</v>
+        <v>0.1893</v>
       </c>
       <c r="D4" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0122</v>
+        <v>0.02</v>
       </c>
       <c r="F4" t="n">
         <v>0.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05</v>
+        <v>0.1488</v>
       </c>
       <c r="H4" t="n">
         <v>0.0223</v>
       </c>
       <c r="I4" t="n">
-        <v>6937239</v>
+        <v>8885520</v>
       </c>
       <c r="J4" t="n">
         <v>516578</v>
@@ -6249,25 +6249,25 @@
         <v>0.065</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0565</v>
+        <v>0.134</v>
       </c>
       <c r="D5" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.015</v>
+        <v>0.0701</v>
       </c>
       <c r="F5" t="n">
         <v>0.5127</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05</v>
+        <v>0.1068</v>
       </c>
       <c r="H5" t="n">
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>5338991</v>
+        <v>2252657</v>
       </c>
       <c r="J5" t="n">
         <v>130963</v>
@@ -6286,25 +6286,25 @@
         <v>0.05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5962</v>
+        <v>0.1445</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1833</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="n">
         <v>0.0261</v>
       </c>
       <c r="I6" t="n">
-        <v>11562</v>
+        <v>367810</v>
       </c>
       <c r="J6" t="n">
         <v>21383</v>
@@ -6415,7 +6415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="5">
@@ -6473,46 +6473,6 @@
       </c>
       <c r="B6" t="n">
         <v>42</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>growth_u</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>leontief_damping</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>B_smoothing_lambda</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dynamic_fixed_costs</t>
-        </is>
-      </c>
-      <c r="B10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6611,31 +6571,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>112.88</v>
+        <v>2365.34</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8955</v>
+        <v>0.9096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.031803</v>
+        <v>0.030285</v>
       </c>
       <c r="E2" t="n">
-        <v>6.93</v>
+        <v>6.6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.058976</v>
+        <v>0.059022</v>
       </c>
       <c r="G2" t="n">
-        <v>0.021792</v>
+        <v>0.021701</v>
       </c>
       <c r="H2" t="n">
-        <v>0.258847</v>
+        <v>0.25703</v>
       </c>
       <c r="I2" t="n">
-        <v>0.020112</v>
+        <v>0.02023</v>
       </c>
       <c r="J2" t="n">
-        <v>0.005332</v>
+        <v>0.005321</v>
       </c>
       <c r="K2" t="n">
         <v>0.000175</v>
@@ -6658,31 +6618,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>50.38</v>
+        <v>806.67</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9223</v>
+        <v>0.9368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014193</v>
+        <v>0.010328</v>
       </c>
       <c r="E3" t="n">
-        <v>3.09</v>
+        <v>2.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.062843</v>
+        <v>0.062893</v>
       </c>
       <c r="G3" t="n">
-        <v>0.022591</v>
+        <v>0.022498</v>
       </c>
       <c r="H3" t="n">
-        <v>0.173891</v>
+        <v>0.17267</v>
       </c>
       <c r="I3" t="n">
-        <v>0.018146</v>
+        <v>0.018253</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004008</v>
+        <v>0.004</v>
       </c>
       <c r="K3" t="n">
         <v>0.000175</v>
@@ -6705,31 +6665,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>147.5</v>
+        <v>3378.76</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9817</v>
+        <v>0.9972</v>
       </c>
       <c r="D4" t="n">
-        <v>0.041554</v>
+        <v>0.043261</v>
       </c>
       <c r="E4" t="n">
-        <v>9.06</v>
+        <v>9.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06403300000000001</v>
+        <v>0.064084</v>
       </c>
       <c r="G4" t="n">
-        <v>0.023017</v>
+        <v>0.022921</v>
       </c>
       <c r="H4" t="n">
-        <v>0.188817</v>
+        <v>0.187492</v>
       </c>
       <c r="I4" t="n">
-        <v>0.018755</v>
+        <v>0.018865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003887</v>
+        <v>0.003879</v>
       </c>
       <c r="K4" t="n">
         <v>0.000175</v>
@@ -6752,31 +6712,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>165.32</v>
+        <v>3933.78</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8137</v>
+        <v>0.8265</v>
       </c>
       <c r="D5" t="n">
-        <v>0.046575</v>
+        <v>0.050367</v>
       </c>
       <c r="E5" t="n">
-        <v>10.15</v>
+        <v>10.98</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06482599999999999</v>
+        <v>0.06487800000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.024168</v>
+        <v>0.024068</v>
       </c>
       <c r="H5" t="n">
-        <v>0.180866</v>
+        <v>0.179596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.019442</v>
+        <v>0.019556</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005127</v>
+        <v>0.005116</v>
       </c>
       <c r="K5" t="n">
         <v>0.000175</v>
@@ -6799,31 +6759,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.16</v>
+        <v>389.19</v>
       </c>
       <c r="C6" t="n">
-        <v>0.778</v>
+        <v>0.7902</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008215999999999999</v>
+        <v>0.004983</v>
       </c>
       <c r="E6" t="n">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05462</v>
+        <v>0.054663</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029803</v>
+        <v>0.029679</v>
       </c>
       <c r="H6" t="n">
-        <v>0.196031</v>
+        <v>0.194655</v>
       </c>
       <c r="I6" t="n">
-        <v>0.029829</v>
+        <v>0.030004</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003487</v>
+        <v>0.00348</v>
       </c>
       <c r="K6" t="n">
         <v>0.000175</v>
@@ -6846,31 +6806,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.04</v>
+        <v>654.03</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.012127</v>
+        <v>0.008373999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.64</v>
+        <v>1.82</v>
       </c>
       <c r="F7" t="n">
-        <v>0.053697</v>
+        <v>0.05374</v>
       </c>
       <c r="G7" t="n">
-        <v>0.024503</v>
+        <v>0.024402</v>
       </c>
       <c r="H7" t="n">
-        <v>0.169058</v>
+        <v>0.167871</v>
       </c>
       <c r="I7" t="n">
-        <v>0.019164</v>
+        <v>0.019276</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0036</v>
+        <v>0.003593</v>
       </c>
       <c r="K7" t="n">
         <v>0.000175</v>
@@ -6893,31 +6853,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101.52</v>
+        <v>2053.24</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8361</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0286</v>
+        <v>0.026289</v>
       </c>
       <c r="E8" t="n">
-        <v>6.23</v>
+        <v>5.73</v>
       </c>
       <c r="F8" t="n">
-        <v>0.065458</v>
+        <v>0.06551</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02652</v>
+        <v>0.02641</v>
       </c>
       <c r="H8" t="n">
-        <v>0.22861</v>
+        <v>0.227005</v>
       </c>
       <c r="I8" t="n">
-        <v>0.024581</v>
+        <v>0.024725</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004534</v>
+        <v>0.004525</v>
       </c>
       <c r="K8" t="n">
         <v>0.000175</v>
@@ -6940,31 +6900,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77.77</v>
+        <v>1439.3</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1019</v>
+        <v>1.1193</v>
       </c>
       <c r="D9" t="n">
-        <v>0.021911</v>
+        <v>0.018429</v>
       </c>
       <c r="E9" t="n">
-        <v>4.77</v>
+        <v>4.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.055925</v>
+        <v>0.05597</v>
       </c>
       <c r="G9" t="n">
-        <v>0.034107</v>
+        <v>0.033966</v>
       </c>
       <c r="H9" t="n">
-        <v>0.201021</v>
+        <v>0.19961</v>
       </c>
       <c r="I9" t="n">
-        <v>0.018931</v>
+        <v>0.019041</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003881</v>
+        <v>0.003873</v>
       </c>
       <c r="K9" t="n">
         <v>0.000175</v>
@@ -6987,31 +6947,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>93.08</v>
+        <v>1828.89</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9623</v>
+        <v>0.9775</v>
       </c>
       <c r="D10" t="n">
-        <v>0.026223</v>
+        <v>0.023417</v>
       </c>
       <c r="E10" t="n">
-        <v>5.71</v>
+        <v>5.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04753</v>
+        <v>0.047568</v>
       </c>
       <c r="G10" t="n">
-        <v>0.026607</v>
+        <v>0.026497</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166688</v>
+        <v>0.165518</v>
       </c>
       <c r="I10" t="n">
-        <v>0.024927</v>
+        <v>0.025073</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004114</v>
+        <v>0.004106</v>
       </c>
       <c r="K10" t="n">
         <v>0.000175</v>
@@ -7034,31 +6994,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56.36</v>
+        <v>936.8</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1996</v>
+        <v>1.2185</v>
       </c>
       <c r="D11" t="n">
-        <v>0.015877</v>
+        <v>0.011995</v>
       </c>
       <c r="E11" t="n">
-        <v>3.46</v>
+        <v>2.61</v>
       </c>
       <c r="F11" t="n">
-        <v>0.048556</v>
+        <v>0.048595</v>
       </c>
       <c r="G11" t="n">
-        <v>0.031351</v>
+        <v>0.031221</v>
       </c>
       <c r="H11" t="n">
-        <v>0.178468</v>
+        <v>0.177215</v>
       </c>
       <c r="I11" t="n">
-        <v>0.022965</v>
+        <v>0.023099</v>
       </c>
       <c r="J11" t="n">
-        <v>0.004018</v>
+        <v>0.004009</v>
       </c>
       <c r="K11" t="n">
         <v>0.000175</v>
@@ -7081,31 +7041,31 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>159.36</v>
+        <v>3745.92</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1202</v>
+        <v>1.1378</v>
       </c>
       <c r="D12" t="n">
-        <v>0.044896</v>
+        <v>0.047962</v>
       </c>
       <c r="E12" t="n">
-        <v>9.779999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="F12" t="n">
-        <v>0.050139</v>
+        <v>0.050178</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0244</v>
+        <v>0.024299</v>
       </c>
       <c r="H12" t="n">
-        <v>0.217842</v>
+        <v>0.216313</v>
       </c>
       <c r="I12" t="n">
-        <v>0.021173</v>
+        <v>0.021297</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004331</v>
+        <v>0.004322</v>
       </c>
       <c r="K12" t="n">
         <v>0.000175</v>
@@ -7128,31 +7088,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>149.94</v>
+        <v>3453.48</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8874</v>
+        <v>0.9014</v>
       </c>
       <c r="D13" t="n">
-        <v>0.042241</v>
+        <v>0.044218</v>
       </c>
       <c r="E13" t="n">
-        <v>9.210000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.062009</v>
+        <v>0.062059</v>
       </c>
       <c r="G13" t="n">
-        <v>0.027216</v>
+        <v>0.027103</v>
       </c>
       <c r="H13" t="n">
-        <v>0.235677</v>
+        <v>0.234023</v>
       </c>
       <c r="I13" t="n">
-        <v>0.021544</v>
+        <v>0.02167</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005085</v>
+        <v>0.005075</v>
       </c>
       <c r="K13" t="n">
         <v>0.000175</v>
@@ -7175,31 +7135,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>97.81999999999999</v>
+        <v>1954.19</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1994</v>
+        <v>1.2183</v>
       </c>
       <c r="D14" t="n">
-        <v>0.027559</v>
+        <v>0.025021</v>
       </c>
       <c r="E14" t="n">
-        <v>6.01</v>
+        <v>5.45</v>
       </c>
       <c r="F14" t="n">
-        <v>0.058796</v>
+        <v>0.058843</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02434</v>
+        <v>0.024239</v>
       </c>
       <c r="H14" t="n">
-        <v>0.28041</v>
+        <v>0.278441</v>
       </c>
       <c r="I14" t="n">
-        <v>0.019648</v>
+        <v>0.019764</v>
       </c>
       <c r="J14" t="n">
-        <v>0.004174</v>
+        <v>0.004165</v>
       </c>
       <c r="K14" t="n">
         <v>0.000175</v>
@@ -7222,31 +7182,31 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>184.91</v>
+        <v>4567.39</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1829</v>
+        <v>1.2015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.052095</v>
+        <v>0.05848</v>
       </c>
       <c r="E15" t="n">
-        <v>11.35</v>
+        <v>12.74</v>
       </c>
       <c r="F15" t="n">
-        <v>0.063834</v>
+        <v>0.063884</v>
       </c>
       <c r="G15" t="n">
-        <v>0.026676</v>
+        <v>0.026566</v>
       </c>
       <c r="H15" t="n">
-        <v>0.321765</v>
+        <v>0.319507</v>
       </c>
       <c r="I15" t="n">
-        <v>0.023176</v>
+        <v>0.023312</v>
       </c>
       <c r="J15" t="n">
-        <v>0.004535</v>
+        <v>0.004526</v>
       </c>
       <c r="K15" t="n">
         <v>0.000175</v>
@@ -7269,31 +7229,31 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>124.47</v>
+        <v>2694.35</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9325</v>
+        <v>0.9472</v>
       </c>
       <c r="D16" t="n">
-        <v>0.035066</v>
+        <v>0.034498</v>
       </c>
       <c r="E16" t="n">
-        <v>7.64</v>
+        <v>7.52</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05398</v>
+        <v>0.054023</v>
       </c>
       <c r="G16" t="n">
-        <v>0.031838</v>
+        <v>0.031707</v>
       </c>
       <c r="H16" t="n">
-        <v>0.221164</v>
+        <v>0.219611</v>
       </c>
       <c r="I16" t="n">
-        <v>0.020246</v>
+        <v>0.020365</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003027</v>
+        <v>0.003021</v>
       </c>
       <c r="K16" t="n">
         <v>0.000175</v>
@@ -7316,31 +7276,31 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>56.15</v>
+        <v>932.13</v>
       </c>
       <c r="C17" t="n">
-        <v>0.873</v>
+        <v>0.8868</v>
       </c>
       <c r="D17" t="n">
-        <v>0.015818</v>
+        <v>0.011935</v>
       </c>
       <c r="E17" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.058938</v>
+        <v>0.058985</v>
       </c>
       <c r="G17" t="n">
-        <v>0.021661</v>
+        <v>0.021572</v>
       </c>
       <c r="H17" t="n">
-        <v>0.179166</v>
+        <v>0.177908</v>
       </c>
       <c r="I17" t="n">
-        <v>0.018036</v>
+        <v>0.018142</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004087</v>
+        <v>0.004079</v>
       </c>
       <c r="K17" t="n">
         <v>0.000175</v>
@@ -7363,31 +7323,31 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>117.31</v>
+        <v>2489.67</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1095</v>
+        <v>1.127</v>
       </c>
       <c r="D18" t="n">
-        <v>0.033048</v>
+        <v>0.031877</v>
       </c>
       <c r="E18" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06321499999999999</v>
+        <v>0.063266</v>
       </c>
       <c r="G18" t="n">
-        <v>0.029958</v>
+        <v>0.029834</v>
       </c>
       <c r="H18" t="n">
-        <v>0.150948</v>
+        <v>0.149888</v>
       </c>
       <c r="I18" t="n">
-        <v>0.017895</v>
+        <v>0.018</v>
       </c>
       <c r="J18" t="n">
-        <v>0.003628</v>
+        <v>0.003621</v>
       </c>
       <c r="K18" t="n">
         <v>0.000175</v>
@@ -7410,31 +7370,31 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>52.89</v>
+        <v>860.75</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7839</v>
+        <v>0.7962</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0149</v>
+        <v>0.011021</v>
       </c>
       <c r="E19" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0.054944</v>
+        <v>0.054987</v>
       </c>
       <c r="G19" t="n">
-        <v>0.029087</v>
+        <v>0.028966</v>
       </c>
       <c r="H19" t="n">
-        <v>0.216351</v>
+        <v>0.214832</v>
       </c>
       <c r="I19" t="n">
-        <v>0.022245</v>
+        <v>0.022375</v>
       </c>
       <c r="J19" t="n">
-        <v>0.003429</v>
+        <v>0.003422</v>
       </c>
       <c r="K19" t="n">
         <v>0.000175</v>
@@ -7457,31 +7417,31 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>159.27</v>
+        <v>3743.08</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8199</v>
+        <v>0.8329</v>
       </c>
       <c r="D20" t="n">
-        <v>0.044871</v>
+        <v>0.047926</v>
       </c>
       <c r="E20" t="n">
-        <v>9.779999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="F20" t="n">
-        <v>0.061635</v>
+        <v>0.061684</v>
       </c>
       <c r="G20" t="n">
-        <v>0.025675</v>
+        <v>0.025568</v>
       </c>
       <c r="H20" t="n">
-        <v>0.183975</v>
+        <v>0.182684</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02747</v>
+        <v>0.027631</v>
       </c>
       <c r="J20" t="n">
-        <v>0.003609</v>
+        <v>0.003602</v>
       </c>
       <c r="K20" t="n">
         <v>0.000175</v>
@@ -7504,31 +7464,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>91.25</v>
+        <v>1781.06</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7044</v>
+        <v>0.7155</v>
       </c>
       <c r="D21" t="n">
-        <v>0.025707</v>
+        <v>0.022804</v>
       </c>
       <c r="E21" t="n">
-        <v>5.6</v>
+        <v>4.97</v>
       </c>
       <c r="F21" t="n">
-        <v>0.052113</v>
+        <v>0.052155</v>
       </c>
       <c r="G21" t="n">
-        <v>0.022595</v>
+        <v>0.022501</v>
       </c>
       <c r="H21" t="n">
-        <v>0.195281</v>
+        <v>0.19391</v>
       </c>
       <c r="I21" t="n">
-        <v>0.022203</v>
+        <v>0.022333</v>
       </c>
       <c r="J21" t="n">
-        <v>0.003916</v>
+        <v>0.003908</v>
       </c>
       <c r="K21" t="n">
         <v>0.000175</v>
@@ -7551,31 +7511,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>84.15000000000001</v>
+        <v>1598.81</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1722</v>
+        <v>1.1906</v>
       </c>
       <c r="D22" t="n">
-        <v>0.023708</v>
+        <v>0.020471</v>
       </c>
       <c r="E22" t="n">
-        <v>5.17</v>
+        <v>4.46</v>
       </c>
       <c r="F22" t="n">
-        <v>0.054503</v>
+        <v>0.054546</v>
       </c>
       <c r="G22" t="n">
-        <v>0.028373</v>
+        <v>0.028256</v>
       </c>
       <c r="H22" t="n">
-        <v>0.189602</v>
+        <v>0.188271</v>
       </c>
       <c r="I22" t="n">
-        <v>0.021294</v>
+        <v>0.021419</v>
       </c>
       <c r="J22" t="n">
-        <v>0.004724</v>
+        <v>0.004714</v>
       </c>
       <c r="K22" t="n">
         <v>0.000175</v>
@@ -7598,31 +7558,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>62.49</v>
+        <v>1075.09</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0989</v>
+        <v>1.1162</v>
       </c>
       <c r="D23" t="n">
-        <v>0.017605</v>
+        <v>0.013765</v>
       </c>
       <c r="E23" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05435</v>
+        <v>0.054393</v>
       </c>
       <c r="G23" t="n">
-        <v>0.025925</v>
+        <v>0.025818</v>
       </c>
       <c r="H23" t="n">
-        <v>0.203492</v>
+        <v>0.202063</v>
       </c>
       <c r="I23" t="n">
-        <v>0.022626</v>
+        <v>0.022758</v>
       </c>
       <c r="J23" t="n">
-        <v>0.003375</v>
+        <v>0.003368</v>
       </c>
       <c r="K23" t="n">
         <v>0.000175</v>
@@ -7645,31 +7605,31 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>195.79</v>
+        <v>4929.23</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1231</v>
+        <v>1.1408</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05516</v>
+        <v>0.063113</v>
       </c>
       <c r="E24" t="n">
-        <v>12.02</v>
+        <v>13.75</v>
       </c>
       <c r="F24" t="n">
-        <v>0.048102</v>
+        <v>0.048141</v>
       </c>
       <c r="G24" t="n">
-        <v>0.029065</v>
+        <v>0.028944</v>
       </c>
       <c r="H24" t="n">
-        <v>0.243871</v>
+        <v>0.242159</v>
       </c>
       <c r="I24" t="n">
-        <v>0.026367</v>
+        <v>0.026522</v>
       </c>
       <c r="J24" t="n">
-        <v>0.004136</v>
+        <v>0.004128</v>
       </c>
       <c r="K24" t="n">
         <v>0.000175</v>
@@ -7692,31 +7652,31 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>85.7</v>
+        <v>1638.08</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1684</v>
+        <v>1.1869</v>
       </c>
       <c r="D25" t="n">
-        <v>0.024143</v>
+        <v>0.020974</v>
       </c>
       <c r="E25" t="n">
-        <v>5.26</v>
+        <v>4.57</v>
       </c>
       <c r="F25" t="n">
-        <v>0.061915</v>
+        <v>0.061964</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02816</v>
+        <v>0.028043</v>
       </c>
       <c r="H25" t="n">
-        <v>0.212789</v>
+        <v>0.211295</v>
       </c>
       <c r="I25" t="n">
-        <v>0.022401</v>
+        <v>0.022533</v>
       </c>
       <c r="J25" t="n">
-        <v>0.003829</v>
+        <v>0.003821</v>
       </c>
       <c r="K25" t="n">
         <v>0.000175</v>
@@ -7739,31 +7699,31 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>72.70999999999999</v>
+        <v>1315.86</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9907</v>
       </c>
       <c r="D26" t="n">
-        <v>0.020486</v>
+        <v>0.016848</v>
       </c>
       <c r="E26" t="n">
-        <v>4.46</v>
+        <v>3.67</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05364</v>
+        <v>0.053683</v>
       </c>
       <c r="G26" t="n">
-        <v>0.035691</v>
+        <v>0.035543</v>
       </c>
       <c r="H26" t="n">
-        <v>0.202948</v>
+        <v>0.201523</v>
       </c>
       <c r="I26" t="n">
-        <v>0.020381</v>
+        <v>0.0205</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00392</v>
+        <v>0.003912</v>
       </c>
       <c r="K26" t="n">
         <v>0.000175</v>
@@ -7786,31 +7746,31 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>76.12</v>
+        <v>1398.56</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0412</v>
+        <v>1.0577</v>
       </c>
       <c r="D27" t="n">
-        <v>0.021444</v>
+        <v>0.017907</v>
       </c>
       <c r="E27" t="n">
-        <v>4.67</v>
+        <v>3.9</v>
       </c>
       <c r="F27" t="n">
-        <v>0.057661</v>
+        <v>0.057707</v>
       </c>
       <c r="G27" t="n">
-        <v>0.027078</v>
+        <v>0.026966</v>
       </c>
       <c r="H27" t="n">
-        <v>0.177931</v>
+        <v>0.176682</v>
       </c>
       <c r="I27" t="n">
-        <v>0.025589</v>
+        <v>0.025739</v>
       </c>
       <c r="J27" t="n">
-        <v>0.004786</v>
+        <v>0.004776</v>
       </c>
       <c r="K27" t="n">
         <v>0.000175</v>
@@ -7833,31 +7793,31 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>129.4</v>
+        <v>2837.71</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7839</v>
+        <v>0.7962</v>
       </c>
       <c r="D28" t="n">
-        <v>0.036456</v>
+        <v>0.036334</v>
       </c>
       <c r="E28" t="n">
-        <v>7.94</v>
+        <v>7.92</v>
       </c>
       <c r="F28" t="n">
-        <v>0.061857</v>
+        <v>0.061906</v>
       </c>
       <c r="G28" t="n">
-        <v>0.024073</v>
+        <v>0.023974</v>
       </c>
       <c r="H28" t="n">
-        <v>0.161667</v>
+        <v>0.160532</v>
       </c>
       <c r="I28" t="n">
-        <v>0.023116</v>
+        <v>0.023252</v>
       </c>
       <c r="J28" t="n">
-        <v>0.004463</v>
+        <v>0.004454</v>
       </c>
       <c r="K28" t="n">
         <v>0.000175</v>
@@ -7880,31 +7840,31 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>117.07</v>
+        <v>2483.09</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7687</v>
+        <v>0.7808</v>
       </c>
       <c r="D29" t="n">
-        <v>0.032983</v>
+        <v>0.031793</v>
       </c>
       <c r="E29" t="n">
-        <v>7.19</v>
+        <v>6.93</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06154</v>
+        <v>0.061589</v>
       </c>
       <c r="G29" t="n">
-        <v>0.028833</v>
+        <v>0.028714</v>
       </c>
       <c r="H29" t="n">
-        <v>0.193214</v>
+        <v>0.191857</v>
       </c>
       <c r="I29" t="n">
-        <v>0.027292</v>
+        <v>0.027452</v>
       </c>
       <c r="J29" t="n">
-        <v>0.005032</v>
+        <v>0.005022</v>
       </c>
       <c r="K29" t="n">
         <v>0.000175</v>
@@ -7927,31 +7887,31 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>120.44</v>
+        <v>2578.83</v>
       </c>
       <c r="C30" t="n">
-        <v>1.101</v>
+        <v>1.1184</v>
       </c>
       <c r="D30" t="n">
-        <v>0.033932</v>
+        <v>0.033019</v>
       </c>
       <c r="E30" t="n">
-        <v>7.39</v>
+        <v>7.2</v>
       </c>
       <c r="F30" t="n">
-        <v>0.063594</v>
+        <v>0.06364400000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02901</v>
+        <v>0.028889</v>
       </c>
       <c r="H30" t="n">
-        <v>0.206165</v>
+        <v>0.204717</v>
       </c>
       <c r="I30" t="n">
-        <v>0.02228</v>
+        <v>0.022411</v>
       </c>
       <c r="J30" t="n">
-        <v>0.004023</v>
+        <v>0.004015</v>
       </c>
       <c r="K30" t="n">
         <v>0.000175</v>
@@ -7974,31 +7934,31 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>121.76</v>
+        <v>2616.42</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9827</v>
+        <v>0.9982</v>
       </c>
       <c r="D31" t="n">
-        <v>0.034302</v>
+        <v>0.0335</v>
       </c>
       <c r="E31" t="n">
-        <v>7.48</v>
+        <v>7.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.056709</v>
+        <v>0.056754</v>
       </c>
       <c r="G31" t="n">
-        <v>0.034415</v>
+        <v>0.034273</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27095</v>
+        <v>0.269047</v>
       </c>
       <c r="I31" t="n">
-        <v>0.018039</v>
+        <v>0.018145</v>
       </c>
       <c r="J31" t="n">
-        <v>0.003709</v>
+        <v>0.003702</v>
       </c>
       <c r="K31" t="n">
         <v>0.000175</v>
@@ -8021,31 +7981,31 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>339.85</v>
+        <v>10282.74</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0391</v>
+        <v>1.0555</v>
       </c>
       <c r="D32" t="n">
-        <v>0.095747</v>
+        <v>0.131659</v>
       </c>
       <c r="E32" t="n">
-        <v>20.87</v>
+        <v>28.69</v>
       </c>
       <c r="F32" t="n">
-        <v>0.054012</v>
+        <v>0.054055</v>
       </c>
       <c r="G32" t="n">
-        <v>0.031814</v>
+        <v>0.031682</v>
       </c>
       <c r="H32" t="n">
-        <v>0.211936</v>
+        <v>0.210448</v>
       </c>
       <c r="I32" t="n">
-        <v>0.017655</v>
+        <v>0.017758</v>
       </c>
       <c r="J32" t="n">
-        <v>0.003981</v>
+        <v>0.003973</v>
       </c>
       <c r="K32" t="n">
         <v>0.000175</v>
@@ -8068,31 +8028,31 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>73.68000000000001</v>
+        <v>1339.13</v>
       </c>
       <c r="C33" t="n">
-        <v>1.159</v>
+        <v>1.1773</v>
       </c>
       <c r="D33" t="n">
-        <v>0.020757</v>
+        <v>0.017146</v>
       </c>
       <c r="E33" t="n">
-        <v>4.52</v>
+        <v>3.74</v>
       </c>
       <c r="F33" t="n">
-        <v>0.056869</v>
+        <v>0.056914</v>
       </c>
       <c r="G33" t="n">
-        <v>0.029611</v>
+        <v>0.029489</v>
       </c>
       <c r="H33" t="n">
-        <v>0.240845</v>
+        <v>0.239154</v>
       </c>
       <c r="I33" t="n">
-        <v>0.027767</v>
+        <v>0.02793</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00427</v>
+        <v>0.004261</v>
       </c>
       <c r="K33" t="n">
         <v>0.000175</v>
@@ -8206,28 +8166,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06</v>
+        <v>16945.15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7399</v>
+        <v>0.8116</v>
       </c>
       <c r="D2" t="n">
-        <v>0.030352</v>
+        <v>0.023959</v>
       </c>
       <c r="E2" t="n">
-        <v>71.01000000000001</v>
+        <v>56.05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.129442</v>
+        <v>0.130131</v>
       </c>
       <c r="G2" t="n">
-        <v>0.249165</v>
+        <v>0.251655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06764100000000001</v>
+        <v>0.067702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.032588</v>
+        <v>0.032967</v>
       </c>
       <c r="J2" t="n">
         <v>5.7e-05</v>
@@ -8253,31 +8213,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03</v>
+        <v>6179.35</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0567</v>
+        <v>1.159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014243</v>
+        <v>0.008737</v>
       </c>
       <c r="E3" t="n">
-        <v>33.32</v>
+        <v>20.44</v>
       </c>
       <c r="F3" t="n">
-        <v>0.108951</v>
+        <v>0.109531</v>
       </c>
       <c r="G3" t="n">
-        <v>0.208359</v>
+        <v>0.210441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.091712</v>
+        <v>0.091793</v>
       </c>
       <c r="I3" t="n">
-        <v>0.032764</v>
+        <v>0.033145</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4e-05</v>
+        <v>5.5e-05</v>
       </c>
       <c r="K3" t="n">
         <v>0.000175</v>
@@ -8300,31 +8260,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05</v>
+        <v>15817.47</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7877</v>
+        <v>0.864</v>
       </c>
       <c r="D4" t="n">
-        <v>0.028824</v>
+        <v>0.022365</v>
       </c>
       <c r="E4" t="n">
-        <v>67.44</v>
+        <v>52.32</v>
       </c>
       <c r="F4" t="n">
-        <v>0.103389</v>
+        <v>0.103939</v>
       </c>
       <c r="G4" t="n">
-        <v>0.21688</v>
+        <v>0.219047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.080447</v>
+        <v>0.08051800000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.027641</v>
+        <v>0.027962</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1e-05</v>
+        <v>6.2e-05</v>
       </c>
       <c r="K4" t="n">
         <v>0.000175</v>
@@ -8347,28 +8307,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06</v>
+        <v>17660.06</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1948</v>
+        <v>1.3105</v>
       </c>
       <c r="D5" t="n">
-        <v>0.031307</v>
+        <v>0.02497</v>
       </c>
       <c r="E5" t="n">
-        <v>73.25</v>
+        <v>58.42</v>
       </c>
       <c r="F5" t="n">
-        <v>0.146062</v>
+        <v>0.146839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.186906</v>
+        <v>0.188774</v>
       </c>
       <c r="H5" t="n">
-        <v>0.065833</v>
+        <v>0.06589200000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.030774</v>
+        <v>0.031131</v>
       </c>
       <c r="J5" t="n">
         <v>7.4e-05</v>
@@ -8394,31 +8354,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.23</v>
+        <v>110244.68</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8862</v>
+        <v>0.972</v>
       </c>
       <c r="D6" t="n">
-        <v>0.123643</v>
+        <v>0.155877</v>
       </c>
       <c r="E6" t="n">
-        <v>289.28</v>
+        <v>364.69</v>
       </c>
       <c r="F6" t="n">
-        <v>0.127074</v>
+        <v>0.12775</v>
       </c>
       <c r="G6" t="n">
-        <v>0.208174</v>
+        <v>0.210254</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06279700000000001</v>
+        <v>0.06285300000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.030751</v>
+        <v>0.031108</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4e-05</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="K6" t="n">
         <v>0.000175</v>
@@ -8441,28 +8401,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.16</v>
+        <v>66035.91</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7863</v>
+        <v>0.8625</v>
       </c>
       <c r="D7" t="n">
-        <v>0.084186</v>
+        <v>0.09336899999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>196.96</v>
+        <v>218.45</v>
       </c>
       <c r="F7" t="n">
-        <v>0.131286</v>
+        <v>0.131985</v>
       </c>
       <c r="G7" t="n">
-        <v>0.266014</v>
+        <v>0.268672</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07346999999999999</v>
+        <v>0.073536</v>
       </c>
       <c r="I7" t="n">
-        <v>0.033325</v>
+        <v>0.033712</v>
       </c>
       <c r="J7" t="n">
         <v>7.2e-05</v>
@@ -8488,28 +8448,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03</v>
+        <v>7434.48</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2526</v>
+        <v>1.3739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.016362</v>
+        <v>0.010512</v>
       </c>
       <c r="E8" t="n">
-        <v>38.28</v>
+        <v>24.59</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09403499999999999</v>
+        <v>0.094536</v>
       </c>
       <c r="G8" t="n">
-        <v>0.238875</v>
+        <v>0.241261</v>
       </c>
       <c r="H8" t="n">
-        <v>0.060915</v>
+        <v>0.060969</v>
       </c>
       <c r="I8" t="n">
-        <v>0.036553</v>
+        <v>0.036978</v>
       </c>
       <c r="J8" t="n">
         <v>5.6e-05</v>
@@ -8535,28 +8495,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04</v>
+        <v>11690.97</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7993</v>
+        <v>0.8767</v>
       </c>
       <c r="D9" t="n">
-        <v>0.022977</v>
+        <v>0.01653</v>
       </c>
       <c r="E9" t="n">
-        <v>53.76</v>
+        <v>38.67</v>
       </c>
       <c r="F9" t="n">
-        <v>0.140397</v>
+        <v>0.141144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.283833</v>
+        <v>0.286669</v>
       </c>
       <c r="H9" t="n">
-        <v>0.066108</v>
+        <v>0.066167</v>
       </c>
       <c r="I9" t="n">
-        <v>0.026843</v>
+        <v>0.027155</v>
       </c>
       <c r="J9" t="n">
         <v>4.9e-05</v>
@@ -8582,31 +8542,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02</v>
+        <v>4562.95</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8708</v>
+        <v>0.9552</v>
       </c>
       <c r="D10" t="n">
-        <v>0.011346</v>
+        <v>0.006452</v>
       </c>
       <c r="E10" t="n">
-        <v>26.54</v>
+        <v>15.09</v>
       </c>
       <c r="F10" t="n">
-        <v>0.13078</v>
+        <v>0.131476</v>
       </c>
       <c r="G10" t="n">
-        <v>0.261165</v>
+        <v>0.263775</v>
       </c>
       <c r="H10" t="n">
-        <v>0.076613</v>
+        <v>0.076681</v>
       </c>
       <c r="I10" t="n">
-        <v>0.030878</v>
+        <v>0.031237</v>
       </c>
       <c r="J10" t="n">
-        <v>6.9e-05</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="K10" t="n">
         <v>0.000175</v>
@@ -8629,31 +8589,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04</v>
+        <v>9172.02</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7922</v>
+        <v>0.8689</v>
       </c>
       <c r="D11" t="n">
-        <v>0.019154</v>
+        <v>0.012968</v>
       </c>
       <c r="E11" t="n">
-        <v>44.81</v>
+        <v>30.34</v>
       </c>
       <c r="F11" t="n">
-        <v>0.103419</v>
+        <v>0.10397</v>
       </c>
       <c r="G11" t="n">
-        <v>0.233785</v>
+        <v>0.236121</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08694399999999999</v>
+        <v>0.087021</v>
       </c>
       <c r="I11" t="n">
-        <v>0.039292</v>
+        <v>0.039748</v>
       </c>
       <c r="J11" t="n">
-        <v>6.4e-05</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="K11" t="n">
         <v>0.000175</v>
@@ -8676,28 +8636,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06</v>
+        <v>18938.69</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7693</v>
+        <v>0.8438</v>
       </c>
       <c r="D12" t="n">
-        <v>0.032993</v>
+        <v>0.026778</v>
       </c>
       <c r="E12" t="n">
-        <v>77.19</v>
+        <v>62.65</v>
       </c>
       <c r="F12" t="n">
-        <v>0.113821</v>
+        <v>0.114427</v>
       </c>
       <c r="G12" t="n">
-        <v>0.284329</v>
+        <v>0.28717</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0801</v>
+        <v>0.08017100000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.028142</v>
+        <v>0.028469</v>
       </c>
       <c r="J12" t="n">
         <v>7.4e-05</v>
@@ -8723,31 +8683,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1</v>
+        <v>38605.93</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7127</v>
+        <v>0.7817</v>
       </c>
       <c r="D13" t="n">
-        <v>0.056285</v>
+        <v>0.054586</v>
       </c>
       <c r="E13" t="n">
-        <v>131.68</v>
+        <v>127.71</v>
       </c>
       <c r="F13" t="n">
-        <v>0.127092</v>
+        <v>0.127769</v>
       </c>
       <c r="G13" t="n">
-        <v>0.233782</v>
+        <v>0.236118</v>
       </c>
       <c r="H13" t="n">
-        <v>0.051846</v>
+        <v>0.051892</v>
       </c>
       <c r="I13" t="n">
-        <v>0.027812</v>
+        <v>0.028135</v>
       </c>
       <c r="J13" t="n">
-        <v>7.6e-05</v>
+        <v>7.7e-05</v>
       </c>
       <c r="K13" t="n">
         <v>0.000175</v>
@@ -8770,31 +8730,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03</v>
+        <v>8210.85</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7332</v>
+        <v>0.8042</v>
       </c>
       <c r="D14" t="n">
-        <v>0.017628</v>
+        <v>0.011609</v>
       </c>
       <c r="E14" t="n">
-        <v>41.24</v>
+        <v>27.16</v>
       </c>
       <c r="F14" t="n">
-        <v>0.123128</v>
+        <v>0.123784</v>
       </c>
       <c r="G14" t="n">
-        <v>0.247829</v>
+        <v>0.250305</v>
       </c>
       <c r="H14" t="n">
-        <v>0.076525</v>
+        <v>0.07659299999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.032432</v>
+        <v>0.032809</v>
       </c>
       <c r="J14" t="n">
-        <v>6.999999999999999e-05</v>
+        <v>7.1e-05</v>
       </c>
       <c r="K14" t="n">
         <v>0.000175</v>
@@ -8817,31 +8777,31 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03</v>
+        <v>8718.139999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8048</v>
+        <v>0.8827</v>
       </c>
       <c r="D15" t="n">
-        <v>0.018438</v>
+        <v>0.012327</v>
       </c>
       <c r="E15" t="n">
-        <v>43.14</v>
+        <v>28.84</v>
       </c>
       <c r="F15" t="n">
-        <v>0.116925</v>
+        <v>0.117547</v>
       </c>
       <c r="G15" t="n">
-        <v>0.20936</v>
+        <v>0.211452</v>
       </c>
       <c r="H15" t="n">
-        <v>0.073904</v>
+        <v>0.07396999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.035711</v>
+        <v>0.036126</v>
       </c>
       <c r="J15" t="n">
-        <v>7.7e-05</v>
+        <v>7.8e-05</v>
       </c>
       <c r="K15" t="n">
         <v>0.000175</v>
@@ -8864,31 +8824,31 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01</v>
+        <v>2640.3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.732</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.007527</v>
+        <v>0.003733</v>
       </c>
       <c r="E16" t="n">
-        <v>17.61</v>
+        <v>8.73</v>
       </c>
       <c r="F16" t="n">
-        <v>0.120281</v>
+        <v>0.120921</v>
       </c>
       <c r="G16" t="n">
-        <v>0.22108</v>
+        <v>0.223289</v>
       </c>
       <c r="H16" t="n">
-        <v>0.077793</v>
+        <v>0.077862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.031516</v>
+        <v>0.031882</v>
       </c>
       <c r="J16" t="n">
-        <v>7.1e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="K16" t="n">
         <v>0.000175</v>
@@ -8911,28 +8871,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05</v>
+        <v>12917.59</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0547</v>
+        <v>1.1568</v>
       </c>
       <c r="D17" t="n">
-        <v>0.024762</v>
+        <v>0.018264</v>
       </c>
       <c r="E17" t="n">
-        <v>57.93</v>
+        <v>42.73</v>
       </c>
       <c r="F17" t="n">
-        <v>0.117632</v>
+        <v>0.118258</v>
       </c>
       <c r="G17" t="n">
-        <v>0.197143</v>
+        <v>0.199112</v>
       </c>
       <c r="H17" t="n">
-        <v>0.093167</v>
+        <v>0.09325</v>
       </c>
       <c r="I17" t="n">
-        <v>0.038403</v>
+        <v>0.038849</v>
       </c>
       <c r="J17" t="n">
         <v>7.499999999999999e-05</v>
@@ -8958,28 +8918,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.03</v>
+        <v>6288.93</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1084</v>
+        <v>1.2158</v>
       </c>
       <c r="D18" t="n">
-        <v>0.014432</v>
+        <v>0.008892000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>33.77</v>
+        <v>20.8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.124991</v>
+        <v>0.125656</v>
       </c>
       <c r="G18" t="n">
-        <v>0.25391</v>
+        <v>0.256447</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05365</v>
+        <v>0.053698</v>
       </c>
       <c r="I18" t="n">
-        <v>0.035777</v>
+        <v>0.036193</v>
       </c>
       <c r="J18" t="n">
         <v>6.2e-05</v>
@@ -9005,28 +8965,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.04</v>
+        <v>9632.780000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9362</v>
+        <v>1.0268</v>
       </c>
       <c r="D19" t="n">
-        <v>0.019871</v>
+        <v>0.01362</v>
       </c>
       <c r="E19" t="n">
-        <v>46.49</v>
+        <v>31.87</v>
       </c>
       <c r="F19" t="n">
-        <v>0.152335</v>
+        <v>0.153145</v>
       </c>
       <c r="G19" t="n">
-        <v>0.183423</v>
+        <v>0.185256</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06690699999999999</v>
+        <v>0.066966</v>
       </c>
       <c r="I19" t="n">
-        <v>0.035697</v>
+        <v>0.036112</v>
       </c>
       <c r="J19" t="n">
         <v>6.7e-05</v>
@@ -9052,28 +9012,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03</v>
+        <v>7295.33</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8908</v>
+        <v>0.977</v>
       </c>
       <c r="D20" t="n">
-        <v>0.016132</v>
+        <v>0.010315</v>
       </c>
       <c r="E20" t="n">
-        <v>37.74</v>
+        <v>24.13</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08312600000000001</v>
+        <v>0.083568</v>
       </c>
       <c r="G20" t="n">
-        <v>0.246138</v>
+        <v>0.248598</v>
       </c>
       <c r="H20" t="n">
-        <v>0.079886</v>
+        <v>0.079957</v>
       </c>
       <c r="I20" t="n">
-        <v>0.034189</v>
+        <v>0.034586</v>
       </c>
       <c r="J20" t="n">
         <v>7.1e-05</v>
@@ -9099,28 +9059,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.05</v>
+        <v>13644.18</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0027</v>
+        <v>1.0998</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0258</v>
+        <v>0.019292</v>
       </c>
       <c r="E21" t="n">
-        <v>60.36</v>
+        <v>45.13</v>
       </c>
       <c r="F21" t="n">
-        <v>0.117899</v>
+        <v>0.118527</v>
       </c>
       <c r="G21" t="n">
-        <v>0.212713</v>
+        <v>0.214838</v>
       </c>
       <c r="H21" t="n">
-        <v>0.057669</v>
+        <v>0.057721</v>
       </c>
       <c r="I21" t="n">
-        <v>0.044609</v>
+        <v>0.045127</v>
       </c>
       <c r="J21" t="n">
         <v>7.8e-05</v>
@@ -9146,28 +9106,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02</v>
+        <v>3605.79</v>
       </c>
       <c r="C22" t="n">
-        <v>1.225</v>
+        <v>1.3436</v>
       </c>
       <c r="D22" t="n">
-        <v>0.009509</v>
+        <v>0.005098</v>
       </c>
       <c r="E22" t="n">
-        <v>22.25</v>
+        <v>11.93</v>
       </c>
       <c r="F22" t="n">
-        <v>0.125441</v>
+        <v>0.126108</v>
       </c>
       <c r="G22" t="n">
-        <v>0.260924</v>
+        <v>0.263531</v>
       </c>
       <c r="H22" t="n">
-        <v>0.091227</v>
+        <v>0.091309</v>
       </c>
       <c r="I22" t="n">
-        <v>0.030509</v>
+        <v>0.030863</v>
       </c>
       <c r="J22" t="n">
         <v>6.499999999999999e-05</v>
@@ -9193,31 +9153,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02</v>
+        <v>4549.82</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2107</v>
+        <v>1.3279</v>
       </c>
       <c r="D23" t="n">
-        <v>0.011321</v>
+        <v>0.006433</v>
       </c>
       <c r="E23" t="n">
-        <v>26.49</v>
+        <v>15.05</v>
       </c>
       <c r="F23" t="n">
-        <v>0.127709</v>
+        <v>0.128389</v>
       </c>
       <c r="G23" t="n">
-        <v>0.244979</v>
+        <v>0.247426</v>
       </c>
       <c r="H23" t="n">
-        <v>0.077263</v>
+        <v>0.077332</v>
       </c>
       <c r="I23" t="n">
-        <v>0.023296</v>
+        <v>0.023566</v>
       </c>
       <c r="J23" t="n">
-        <v>7.4e-05</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="K23" t="n">
         <v>0.000175</v>
@@ -9240,31 +9200,31 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.18</v>
+        <v>80811.62</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7261</v>
+        <v>0.7964</v>
       </c>
       <c r="D24" t="n">
-        <v>0.097951</v>
+        <v>0.114261</v>
       </c>
       <c r="E24" t="n">
-        <v>229.16</v>
+        <v>267.32</v>
       </c>
       <c r="F24" t="n">
-        <v>0.115535</v>
+        <v>0.116149</v>
       </c>
       <c r="G24" t="n">
-        <v>0.287619</v>
+        <v>0.290493</v>
       </c>
       <c r="H24" t="n">
-        <v>0.083009</v>
+        <v>0.083083</v>
       </c>
       <c r="I24" t="n">
-        <v>0.040022</v>
+        <v>0.040487</v>
       </c>
       <c r="J24" t="n">
-        <v>6.600000000000001e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K24" t="n">
         <v>0.000175</v>
@@ -9287,28 +9247,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02</v>
+        <v>5252.92</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8089</v>
+        <v>0.8872</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01261</v>
+        <v>0.007427</v>
       </c>
       <c r="E25" t="n">
-        <v>29.5</v>
+        <v>17.38</v>
       </c>
       <c r="F25" t="n">
-        <v>0.093864</v>
+        <v>0.094364</v>
       </c>
       <c r="G25" t="n">
-        <v>0.244241</v>
+        <v>0.246682</v>
       </c>
       <c r="H25" t="n">
-        <v>0.067109</v>
+        <v>0.06716900000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.029375</v>
+        <v>0.029716</v>
       </c>
       <c r="J25" t="n">
         <v>6.8e-05</v>
@@ -9334,31 +9294,31 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03</v>
+        <v>6118.36</v>
       </c>
       <c r="C26" t="n">
-        <v>0.842</v>
+        <v>0.9236</v>
       </c>
       <c r="D26" t="n">
-        <v>0.014138</v>
+        <v>0.008651000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>33.08</v>
+        <v>20.24</v>
       </c>
       <c r="F26" t="n">
-        <v>0.128324</v>
+        <v>0.129007</v>
       </c>
       <c r="G26" t="n">
-        <v>0.172904</v>
+        <v>0.174631</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08260199999999999</v>
+        <v>0.082675</v>
       </c>
       <c r="I26" t="n">
-        <v>0.031976</v>
+        <v>0.032347</v>
       </c>
       <c r="J26" t="n">
-        <v>7.8e-05</v>
+        <v>7.9e-05</v>
       </c>
       <c r="K26" t="n">
         <v>0.000175</v>
@@ -9381,28 +9341,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.15</v>
+        <v>63959.74</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8496</v>
+        <v>0.9319</v>
       </c>
       <c r="D27" t="n">
-        <v>0.082193</v>
+        <v>0.090434</v>
       </c>
       <c r="E27" t="n">
-        <v>192.3</v>
+        <v>211.58</v>
       </c>
       <c r="F27" t="n">
-        <v>0.158295</v>
+        <v>0.159137</v>
       </c>
       <c r="G27" t="n">
-        <v>0.216697</v>
+        <v>0.218862</v>
       </c>
       <c r="H27" t="n">
-        <v>0.08581800000000001</v>
+        <v>0.085895</v>
       </c>
       <c r="I27" t="n">
-        <v>0.038291</v>
+        <v>0.038736</v>
       </c>
       <c r="J27" t="n">
         <v>5.1e-05</v>
@@ -9428,28 +9388,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.29</v>
+        <v>150321.56</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0427</v>
+        <v>1.1437</v>
       </c>
       <c r="D28" t="n">
-        <v>0.156016</v>
+        <v>0.212542</v>
       </c>
       <c r="E28" t="n">
-        <v>365.01</v>
+        <v>497.26</v>
       </c>
       <c r="F28" t="n">
-        <v>0.097055</v>
+        <v>0.097571</v>
       </c>
       <c r="G28" t="n">
-        <v>0.183596</v>
+        <v>0.185431</v>
       </c>
       <c r="H28" t="n">
-        <v>0.075709</v>
+        <v>0.075776</v>
       </c>
       <c r="I28" t="n">
-        <v>0.024741</v>
+        <v>0.025028</v>
       </c>
       <c r="J28" t="n">
         <v>5.7e-05</v>
